--- a/docs/research/provinces/SportsHub-Saskatchewan.xlsx
+++ b/docs/research/provinces/SportsHub-Saskatchewan.xlsx
@@ -11,12 +11,14 @@
     <sheet name="Leagues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Club-League Map" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Contacts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Club Sizes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$108</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$102</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Club Sizes'!$A$1:$C$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -557,8 +559,6 @@
           <t>Biggar</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>recreation@townofbiggar.com</t>
@@ -604,7 +604,6 @@
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -627,8 +626,6 @@
           <t>Carrot River</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>crrb@sasktel.net</t>
@@ -674,7 +671,6 @@
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -697,8 +693,6 @@
           <t>Christopher Lake</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>lwagner@srsd119.ca</t>
@@ -744,7 +738,6 @@
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -767,8 +760,6 @@
           <t>Cumberland House</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>aaronfosseneuve@nlsd113.ca</t>
@@ -841,8 +832,6 @@
           <t>Dundurn</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>sndriedger@hotmail.com</t>
@@ -915,8 +904,6 @@
           <t>Estevan</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>estevanclubbasketball@gmail.com</t>
@@ -947,7 +934,6 @@
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>verified</t>
@@ -985,8 +971,6 @@
           <t>Hafford</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>jillb2@hotmail.com</t>
@@ -1032,7 +1016,6 @@
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1055,8 +1038,6 @@
           <t>Hudson Bay</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>april.danielle@nesd.ca</t>
@@ -1102,7 +1083,6 @@
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1125,15 +1105,11 @@
           <t>Humboldt</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>basketballhumboldt@gmail.com</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
@@ -1149,7 +1125,6 @@
           <t>community nonprofit (club team)</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>reported</t>
@@ -1187,8 +1162,6 @@
           <t>Humboldt</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>bhkusch@hotmail.com</t>
@@ -1261,7 +1234,6 @@
           <t>Indian Head</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>306-550-7645 (Josh Godlien) or 306-695-7420 (Doug Gheyssen)</t>
@@ -1277,7 +1249,6 @@
           <t>https://www.ihactivities.ca</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Community basketball / Jr. NBA programming Gr 2 through Gr 5/6 (boys and girls groups), games at IH Elementary and IH High School</t>
@@ -1335,8 +1306,6 @@
           <t>Kelvington</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Kim.nicholls@horizonsd.ca</t>
@@ -1382,7 +1351,6 @@
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1405,8 +1373,6 @@
           <t>Kindersley</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>jessie_099@hotmail.com</t>
@@ -1479,8 +1445,6 @@
           <t>Langham</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>jennaharder@hotmail.com</t>
@@ -1526,7 +1490,6 @@
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1549,8 +1512,6 @@
           <t>Luseland</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>dan@holmanfarminggroup.com</t>
@@ -1596,7 +1557,6 @@
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1619,7 +1579,6 @@
           <t>Martensville</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>(306) 683-5577</t>
@@ -1630,7 +1589,6 @@
           <t>areddekopp@martensville.ca</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Angie Reddekopp — City of Martensville Recreation Program Supervisor (program lead)</t>
@@ -1651,7 +1609,6 @@
           <t>municipal recreation program / community (BSI member as 'Martensville Basketball')</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>verified</t>
@@ -1689,8 +1646,6 @@
           <t>Meadow Lake</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>alan.robin@nwsd.ca</t>
@@ -1763,8 +1718,6 @@
           <t>Melfort</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>penand00@gmail.com</t>
@@ -1837,27 +1790,21 @@
           <t>Melville</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>mambasclubbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>Club basketball (details not published)</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>primary</t>
@@ -2059,8 +2006,6 @@
           <t>Moose Jaw</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>mjballers18@gmail.com</t>
@@ -2081,13 +2026,11 @@
           <t>Youth basketball program (Facebook group community)</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -2125,27 +2068,21 @@
           <t>Moose Jaw</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>andrews.garry@gmail.com</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>primary</t>
@@ -2183,8 +2120,6 @@
           <t>Moose Jaw</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>mjspartans17@gmail.com</t>
@@ -2215,7 +2150,6 @@
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>verified</t>
@@ -2253,8 +2187,6 @@
           <t>Moose Jaw</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>mjspartans17@gmail.com</t>
@@ -2285,7 +2217,6 @@
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>verified</t>
@@ -2353,13 +2284,11 @@
           <t>Early-childhood intro basketball: Baby Ballers, Little Ballers, Mini Ballers divisions; launched Moose Jaw programming with 100+ signups for free awareness classes</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>private academy (intro program)</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>reported</t>
@@ -2397,27 +2326,21 @@
           <t>Moosomin</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>bdodds@hotmail.com</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Club basketball (details not published)</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>primary</t>
@@ -2455,8 +2378,6 @@
           <t>Nipawin</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>d.seckinger@nipawin.com</t>
@@ -2569,7 +2490,6 @@
           <t>community nonprofit (friendship centre-hosted program)</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>primary</t>
@@ -2607,8 +2527,6 @@
           <t>North Battleford</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>l.sander@hotmail.com</t>
@@ -2763,8 +2681,6 @@
           <t>Outlook</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>amber.thompson@sunwestsd.ca</t>
@@ -2837,8 +2753,6 @@
           <t>Paradise Hill</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>dimples1973fink@gmail.com</t>
@@ -2884,7 +2798,6 @@
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2907,8 +2820,6 @@
           <t>Porcupine Plain</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>boyle.Jocelyn@nesd.ca</t>
@@ -2954,7 +2865,6 @@
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2977,8 +2887,6 @@
           <t>Prince Albert</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>thunderbasketball.sk@gmail.com</t>
@@ -3009,7 +2917,6 @@
           <t>community nonprofit (inclusive rep club)</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>verified</t>
@@ -3211,8 +3118,6 @@
           <t>Rapid View</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>mc_nolin@yahoo.ca</t>
@@ -3258,7 +3163,6 @@
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3281,27 +3185,21 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>https://www.instagram.com/306.heat.basketball/</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3369,7 +3267,6 @@
           <t>Neighbourhood community association (registered charity est. 1987) offering a youth basketball program among social/recreation programs</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
           <t>multi-sport / community nonprofit organization</t>
@@ -3417,8 +3314,6 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>info@reginaballersbasketball.com</t>
@@ -3429,19 +3324,16 @@
           <t>https://reginaballersbasketball.com</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Rep/club teams by birth-year cohorts (2012, 2013, 2014); Canada Basketball Verified club (background checks, Safe Sport)</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3479,8 +3371,6 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>info@reginaballersbasketball.com</t>
@@ -3491,7 +3381,6 @@
           <t>https://reginaballersbasketball.com/</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Rep/club teams organized by birth year (2012, 2013, 2014 team contact emails published); Canada Basketball Verified club</t>
@@ -3507,7 +3396,6 @@
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>verified</t>
@@ -3545,15 +3433,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>gottsela@hotmail.com</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Club/rep teams, grades ~6-8 evidenced</t>
@@ -3569,7 +3453,6 @@
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3607,23 +3490,16 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3661,19 +3537,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
           <t>club (unspecified)</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -3716,7 +3584,6 @@
           <t>Scott Collegiate, North Central Regina (program venue)</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>firstnationsbasketball@gmail.com</t>
@@ -3737,13 +3604,11 @@
           <t>Indigenous youth program: basketball camps, U18 club teams (Team FN Gold, Team FN Silver), prep team; integrates Cree language and Indigenous teachings</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>community nonprofit (Indigenous youth club)</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>verified</t>
@@ -3781,8 +3646,6 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>firstnationsbasketball@gmail.com</t>
@@ -3803,13 +3666,11 @@
           <t>Indigenous-focused basketball training + life lessons through cultural teachings; camps and sessions for Grade 5 through high school; started 2021; planning on-reserve camps and U19 Indigenous Games team</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>private academy (Indigenous-focused training organization)</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>verified</t>
@@ -3959,7 +3820,6 @@
           <t>Camps and training: Gr 1-4 Training Ground (Sept-Nov), summer camps, seasonal skills programs</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>private academy (camps/training)</t>
@@ -4007,8 +3867,6 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>jeremy.sundeen@gmail.com</t>
@@ -4039,7 +3897,6 @@
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4077,8 +3934,6 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>mericbauda@gmail.com</t>
@@ -4089,19 +3944,16 @@
           <t>https://www.instagram.com/yqr.novaelite/</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>club (unspecified)</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -4139,27 +3991,21 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>prairiedreambasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4197,11 +4043,6 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>Club/rep teams (Boys Grade 7/8 evidenced)</t>
@@ -4217,7 +4058,6 @@
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4255,15 +4095,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>queencitysplash@gmail.com</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>Club/rep teams (Boys Grade 7/8 evidenced)</t>
@@ -4279,7 +4115,6 @@
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4317,15 +4152,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>cdandresfamily@gmail.com</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>Club/rep teams (Boys Grade 7/8 evidenced)</t>
@@ -4341,7 +4172,6 @@
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4379,13 +4209,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>306-584-3222</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>https://www.rcba.ca</t>
@@ -4453,27 +4281,21 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>reginamambasclub@gmail.com</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>Youth club (players ~12-13 as of 2019 CBC story); started as a Grade 5 group</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>reported</t>
@@ -4511,7 +4333,6 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>306-596-1470</t>
@@ -4527,19 +4348,16 @@
           <t>https://www.reginaraptors.ca/</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4577,23 +4395,16 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4631,8 +4442,6 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>kev@riseabovebasketball.ca</t>
@@ -4643,19 +4452,16 @@
           <t>https://riseabovebasketballacademy.ca</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>Club basketball 9U-17U/High School divisions; teams travel to Edmonton, Calgary, Dawson Creek, Peace River, Fort St. John tournaments</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>private academy/club</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -4693,23 +4499,16 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>k_bellefleur@hotmail.com</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
           <t>club (unspecified)</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -4747,27 +4546,21 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>saskskybasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4805,27 +4598,21 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>k_bellefleur@hotmail.com</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4868,26 +4655,21 @@
           <t>200-235 12th Ave E, Regina, SK S4N 6B3</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>https://www.shoot360.com/regina</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>Immersive tech-driven basketball training (in-person coaching + digital gamification); facility opening 2026 — programs/hours listed as coming soon</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>private academy (franchise training facility)</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4925,7 +4707,6 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>(306)-527-9241</t>
@@ -4951,13 +4732,11 @@
           <t>Training academy 25+ years: skill sessions, player development, youth league play combining gameplay with structured training; Soldiers Academy sessions run at SASKHOMECOURT facility</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>primary</t>
@@ -4995,7 +4774,6 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>306-527-9241</t>
@@ -5011,13 +4789,11 @@
           <t>https://www.saskhomecourt.com/soldiers</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>Academy skill-development sessions, private training, own summer league combining gameplay with structured training; funding applications offered for participants</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>private academy</t>
@@ -5065,27 +4841,21 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>m.stefaniuk@sasktel.net</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5123,23 +4893,16 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>m.stefaniuk@sasktel.net</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
           <t>club (unspecified)</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -5177,7 +4940,6 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>306-530-5373</t>
@@ -5188,20 +4950,16 @@
           <t>sasktriplethreat@gmail.com</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5239,27 +4997,21 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>ral751@mail.usask.ca</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>primary</t>
@@ -5297,23 +5049,16 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>ral751@mail.usask.ca</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
           <t>club (unspecified)</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -5351,23 +5096,16 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
           <t>club (unspecified)</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -5435,13 +5173,11 @@
           <t>Private training academy since 2010: 1-on-1 and small-group training, Xcite Academy skill development, summer travel teams, community skill camps; youth ages 6-17</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>verified</t>
@@ -5479,8 +5215,6 @@
           <t>Rosetown</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>jkatwhite@gmail.com</t>
@@ -5553,8 +5287,6 @@
           <t>Rosthern</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>Candicebihari@gmail.com</t>
@@ -5600,7 +5332,6 @@
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5623,8 +5354,6 @@
           <t>Sandy Bay</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>atraxel@yahoo.com</t>
@@ -5697,19 +5426,11 @@
           <t>Saskatchewan (regional — base city not published)</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
           <t>club (unspecified)</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -5859,7 +5580,6 @@
           <t>Training 5 days/week for ages 4-17: 1-hour skill sessions (beginner/advanced), Young Stars (ages 4-6), girls-only sessions, open gym, seasonal camps (February break, Easter, Summer, November break, Christmas), pro-level clinics</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
           <t>private academy (branch of Regina-HQ HoopLife Basketball Inc.)</t>
@@ -5907,8 +5627,6 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>houndsvillehoops@gmail.com</t>
@@ -5919,7 +5637,6 @@
           <t>https://www.instagram.com/houndsvillehoops/</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>High-level basketball coaching and elite training; 'Refining Basketball' ages 10-12; 'Levelling Up Basketball' ages 13+; community programming delivered in partnership with Stonebridge Community Association</t>
@@ -5935,7 +5652,6 @@
           <t>private academy (player development / training)</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>reported</t>
@@ -5973,9 +5689,6 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>https://www.facebook.com/onelovebasketball/</t>
@@ -6001,7 +5714,6 @@
           <t>community nonprofit (youth development through basketball)</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>reported</t>
@@ -6044,7 +5756,6 @@
           <t>Unit 10 - 147 Olson Lane West, Saskatoon, SK S7V 0L1</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>info@myrosewood.ca</t>
@@ -6117,7 +5828,6 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>(306) 527-9241</t>
@@ -6133,7 +5843,6 @@
           <t>https://www.saskhomecourt.com/</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>Summer League (Season 6, June 21-Aug 20): grades 4-12 plus post-grad U21 division, A &amp; B skill divisions, $400+tax ($200 post-grad), weeknight games + practices; private training; Soldiers Academy. Venues: U of S PAC &amp; Education Gym, École Canadienne-Française, Martensville Athletic Pavilion</t>
@@ -6191,7 +5900,6 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>+1 639-597-3571</t>
@@ -6227,7 +5935,6 @@
           <t>private academy / club</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>verified</t>
@@ -6347,13 +6054,11 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>(306) 249-4712</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>https://smbayxe.ca</t>
@@ -6421,7 +6126,6 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>306-693-5622</t>
@@ -6447,7 +6151,6 @@
           <t>Paid basketball academy programming for grades 5-8, delivered in partnership with Saskatoon Public Schools (2023-24 listing)</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
           <t>private academy program (school-division partnership; not a varsity team)</t>
@@ -6495,8 +6198,6 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
           <t>saskatoonslam@gmail.com</t>
@@ -6507,7 +6208,6 @@
           <t>https://saskatoonslam.com</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr">
         <is>
           <t>Rep/club teams, boys and girls, U11/U13/U15/U17/U18; multiple teams per age (e.g. 3x U13 girls, 2x U15 girls, 2x U17 girls); hosts Prairie Season Opener tournament</t>
@@ -6565,15 +6265,11 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>https://app.teamlinkt.com/register/go/saskatoonshadowbasketballclub/73399</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
           <t>Nonprofit boys club basketball, U11/U13/U15/U18; annual fall tryouts (2025-season tryout registration ran Sep 2-22, 2024)</t>
@@ -6631,16 +6327,11 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>mitchellda1978@gmail.com</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>BSI-sanctioned club tournament circuit (inferred from BSI club membership)</t>
@@ -6651,7 +6342,6 @@
           <t>club (structure unknown)</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -6694,7 +6384,6 @@
           <t>PO Box 32061 Erindale, Saskatoon, SK S7S 1N8</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>basketball@silverspringcommunity.ca</t>
@@ -6725,7 +6414,6 @@
           <t>community nonprofit (multi-sport community association)</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>reported</t>
@@ -6768,7 +6456,6 @@
           <t>PO Box 23085, Market Mall, Saskatoon, SK S7J 5H3</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
           <t>ourstonebridge.programs@gmail.com</t>
@@ -6841,8 +6528,6 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>stuttersteps.adrian@gmail.com</t>
@@ -6853,7 +6538,6 @@
           <t>https://www.facebook.com/stuttersteps.bball/</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr">
         <is>
           <t>Basketball player development and skill training</t>
@@ -6869,7 +6553,6 @@
           <t>private academy / club (player development)</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
           <t>reported</t>
@@ -6907,8 +6590,6 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>info@basketballexperience.ca</t>
@@ -6981,8 +6662,6 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>info@yxeelitebasketball.com</t>
@@ -7055,8 +6734,6 @@
           <t>Saskatoon (unconfirmed)</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
           <t>info@uprepbasketball.com</t>
@@ -7077,13 +6754,11 @@
           <t>Nonprofit prep/club basketball for student-athletes; coaching staff includes Dion Dobranski (Saskatoon; also founder of YXE Elite)</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
           <t>private prep club (self-described nonprofit)</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -7121,8 +6796,6 @@
           <t>St. Walburg</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>keljenlarre@gmail.com</t>
@@ -7168,7 +6841,6 @@
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7191,8 +6863,6 @@
           <t>Swift Current</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>scminorbasketball@gmail.com</t>
@@ -7203,7 +6873,6 @@
           <t>https://www.swiftcurrentsurge.ca/</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
           <t>Nonprofit founded 2013; competitive 'Surge' rep teams with published tryouts for U11 boys, U15 girls, and Grade 9-12 boys; summer basketball camp; coach recruitment program; serves southwest Saskatchewan</t>
@@ -7261,8 +6930,6 @@
           <t>Tisdale</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
           <t>recreation@tisdale.ca</t>
@@ -7308,7 +6975,6 @@
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7331,8 +6997,6 @@
           <t>Turtleford</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
           <t>marilyn.whelan@nwsd.ca</t>
@@ -7378,7 +7042,6 @@
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7401,8 +7064,6 @@
           <t>Unity</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
           <t>billandcarin_leibel@live.ca</t>
@@ -7448,7 +7109,6 @@
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7553,8 +7213,6 @@
           <t>Warman</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
           <t>smba4712@gmail.com</t>
@@ -7627,8 +7285,6 @@
           <t>Warman</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
           <t>warmanwolves@gmail.com</t>
@@ -7659,7 +7315,6 @@
           <t>community nonprofit (volunteer parent-run club)</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
           <t>primary</t>
@@ -7697,8 +7352,6 @@
           <t>Weyburn</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
           <t>h.souledge@gmail.com</t>
@@ -7771,7 +7424,6 @@
           <t>Yorkton</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>306-621-2595</t>
@@ -7849,27 +7501,21 @@
           <t>Yorkton</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>darcy_zaharia@hotmail.com</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr">
         <is>
           <t>U13 girls community team; first season completed June 2026 (exhibition vs U13 boys Blue Jays); sponsored by Harvest Meats; coach Johanna Fleger; also runs Harvest Hotshots basketball camp</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
           <t>verified</t>
@@ -11361,7 +11007,6 @@
           <t>Biggar</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>recreation@townofbiggar.com</t>
@@ -11389,7 +11034,6 @@
           <t>Carrot River</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>crrb@sasktel.net</t>
@@ -11417,7 +11061,6 @@
           <t>Christopher Lake</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>lwagner@srsd119.ca</t>
@@ -11445,7 +11088,6 @@
           <t>Cumberland House</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>aaronfosseneuve@nlsd113.ca</t>
@@ -11473,7 +11115,6 @@
           <t>Dundurn</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>sndriedger@hotmail.com</t>
@@ -11501,7 +11142,6 @@
           <t>Estevan</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>estevanclubbasketball@gmail.com</t>
@@ -11529,7 +11169,6 @@
           <t>Hafford</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>jillb2@hotmail.com</t>
@@ -11557,7 +11196,6 @@
           <t>Hudson Bay</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>april.danielle@nesd.ca</t>
@@ -11585,14 +11223,11 @@
           <t>Humboldt</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>basketballhumboldt@gmail.com</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11605,7 +11240,6 @@
           <t>Humboldt</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>bhkusch@hotmail.com</t>
@@ -11643,7 +11277,6 @@
           <t>dgheyssen@sasktel.net</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>https://www.ihactivities.ca</t>
@@ -11661,7 +11294,6 @@
           <t>Kelvington</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>Kim.nicholls@horizonsd.ca</t>
@@ -11689,7 +11321,6 @@
           <t>Kindersley</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>jessie_099@hotmail.com</t>
@@ -11717,7 +11348,6 @@
           <t>Langham</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>jennaharder@hotmail.com</t>
@@ -11745,7 +11375,6 @@
           <t>Luseland</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>dan@holmanfarminggroup.com</t>
@@ -11788,7 +11417,6 @@
           <t>Angie Reddekopp — City of Martensville Recreation Program Supervisor (program lead)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11801,7 +11429,6 @@
           <t>Meadow Lake</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>alan.robin@nwsd.ca</t>
@@ -11829,7 +11456,6 @@
           <t>Melfort</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>penand00@gmail.com</t>
@@ -11857,14 +11483,11 @@
           <t>Melville</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>mambasclubbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11941,7 +11564,6 @@
           <t>Moose Jaw</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>mjballers18@gmail.com</t>
@@ -11969,14 +11591,11 @@
           <t>Moose Jaw</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>andrews.garry@gmail.com</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11989,7 +11608,6 @@
           <t>Moose Jaw</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>mjspartans17@gmail.com</t>
@@ -12017,7 +11635,6 @@
           <t>Moose Jaw</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>mjspartans17@gmail.com</t>
@@ -12077,14 +11694,11 @@
           <t>Moosomin</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>bdodds@hotmail.com</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -12097,7 +11711,6 @@
           <t>Nipawin</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>d.seckinger@nipawin.com</t>
@@ -12157,7 +11770,6 @@
           <t>North Battleford</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>l.sander@hotmail.com</t>
@@ -12217,7 +11829,6 @@
           <t>Outlook</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>amber.thompson@sunwestsd.ca</t>
@@ -12245,7 +11856,6 @@
           <t>Paradise Hill</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>dimples1973fink@gmail.com</t>
@@ -12273,7 +11883,6 @@
           <t>Porcupine Plain</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>boyle.Jocelyn@nesd.ca</t>
@@ -12301,7 +11910,6 @@
           <t>Prince Albert</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>thunderbasketball.sk@gmail.com</t>
@@ -12393,7 +12001,6 @@
           <t>Rapid View</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>mc_nolin@yahoo.ca</t>
@@ -12453,13 +12060,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>info@reginaballersbasketball.com</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>https://reginaballersbasketball.com</t>
@@ -12477,13 +12082,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>info@reginaballersbasketball.com</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>https://reginaballersbasketball.com/</t>
@@ -12501,14 +12104,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>gottsela@hotmail.com</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12521,7 +12121,6 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>firstnationsbasketball@gmail.com</t>
@@ -12549,7 +12148,6 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>firstnationsbasketball@gmail.com</t>
@@ -12641,7 +12239,6 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>jeremy.sundeen@gmail.com</t>
@@ -12669,13 +12266,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>mericbauda@gmail.com</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>https://www.instagram.com/yqr.novaelite/</t>
@@ -12693,14 +12288,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>prairiedreambasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -12713,14 +12305,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>queencitysplash@gmail.com</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -12733,14 +12322,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>cdandresfamily@gmail.com</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -12758,7 +12344,6 @@
           <t>306-584-3222</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>Brett Fisher — President; Landon Barr — Executive Director; Tess Rispens-Sisco — Assistant Executive Director</t>
@@ -12781,14 +12366,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>reginamambasclub@gmail.com</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -12811,7 +12393,6 @@
           <t>reginaraptors@gmail.com</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>https://www.reginaraptors.ca/</t>
@@ -12829,13 +12410,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>kev@riseabovebasketball.ca</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>https://riseabovebasketballacademy.ca</t>
@@ -12853,14 +12432,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>k_bellefleur@hotmail.com</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -12873,14 +12449,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>saskskybasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -12893,14 +12466,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>k_bellefleur@hotmail.com</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -12955,7 +12525,6 @@
           <t>homecourtbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>https://www.saskhomecourt.com/soldiers</t>
@@ -12973,14 +12542,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>m.stefaniuk@sasktel.net</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -12993,14 +12559,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>m.stefaniuk@sasktel.net</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -13023,8 +12586,6 @@
           <t>sasktriplethreat@gmail.com</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -13037,14 +12598,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>ral751@mail.usask.ca</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -13057,14 +12615,11 @@
           <t>Regina</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>ral751@mail.usask.ca</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -13109,7 +12664,6 @@
           <t>Rosetown</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>jkatwhite@gmail.com</t>
@@ -13137,7 +12691,6 @@
           <t>Rosthern</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>Candicebihari@gmail.com</t>
@@ -13165,7 +12718,6 @@
           <t>Sandy Bay</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>atraxel@yahoo.com</t>
@@ -13257,13 +12809,11 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>houndsvillehoops@gmail.com</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>https://www.instagram.com/houndsvillehoops/</t>
@@ -13281,8 +12831,6 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>Mike Tanton — Co-Founder</t>
@@ -13305,7 +12853,6 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>info@myrosewood.ca</t>
@@ -13343,7 +12890,6 @@
           <t>homecourtbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>https://www.saskhomecourt.com/</t>
@@ -13430,7 +12976,6 @@
           <t>(306) 249-4712</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>Greg Jockims — President (VP: Brad Smith; directors incl. Riley Daku, Sandy Bresciani, Kory Dawe)</t>
@@ -13485,13 +13030,11 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>saskatoonslam@gmail.com</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>https://saskatoonslam.com</t>
@@ -13509,14 +13052,11 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
           <t>mitchellda1978@gmail.com</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -13529,7 +13069,6 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>basketball@silverspringcommunity.ca</t>
@@ -13557,7 +13096,6 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>ourstonebridge.programs@gmail.com</t>
@@ -13585,13 +13123,11 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>stuttersteps.adrian@gmail.com</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>https://www.facebook.com/stuttersteps.bball/</t>
@@ -13609,7 +13145,6 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>info@basketballexperience.ca</t>
@@ -13637,7 +13172,6 @@
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>info@yxeelitebasketball.com</t>
@@ -13665,7 +13199,6 @@
           <t>Saskatoon (unconfirmed)</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>info@uprepbasketball.com</t>
@@ -13693,7 +13226,6 @@
           <t>St. Walburg</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>keljenlarre@gmail.com</t>
@@ -13721,13 +13253,11 @@
           <t>Swift Current</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>scminorbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>https://www.swiftcurrentsurge.ca/</t>
@@ -13745,7 +13275,6 @@
           <t>Tisdale</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
           <t>recreation@tisdale.ca</t>
@@ -13773,7 +13302,6 @@
           <t>Turtleford</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>marilyn.whelan@nwsd.ca</t>
@@ -13801,7 +13329,6 @@
           <t>Unity</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>billandcarin_leibel@live.ca</t>
@@ -13861,7 +13388,6 @@
           <t>Warman</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>smba4712@gmail.com</t>
@@ -13889,7 +13415,6 @@
           <t>Warman</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>warmanwolves@gmail.com</t>
@@ -13917,7 +13442,6 @@
           <t>Weyburn</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>h.souledge@gmail.com</t>
@@ -13977,17 +13501,936 @@
           <t>Yorkton</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>darcy_zaharia@hotmail.com</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Teams counted (directional)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Breakdown (league=teams)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Dundonald</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=23</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Stonebridge</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=16</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Martensville</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=12</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Evergreen/Aspen Ridge</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=11</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GTBC (Golden Ticket Basketball Club)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Rosewood</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>APC</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=8</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EACCA</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Saskhoops</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Willowgrove</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Lakeview</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Silverwood</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Warman</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Misfits</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Regina Youth Club Basketball League (R=2; BSI Club Championships (Basketball Sas=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Slam (Saskatoon Slam / SLAM Tigers)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Estevan Grizzlies</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Regina Youth Club Basketball League (R=2; BSI Club Championships (Basketball Sas=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Avalon</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Humboldt Heat</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Swift Current Surge</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Queen City Basketball (Splash/Mambas/Black Caps)</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ECP</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>River Heights</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Briarwood</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Silverspring</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>South Nutana Park</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Eastview</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Lawson Heights</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Wildwood</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Varsity View</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Saskatoon Minor Basketball Association=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Queen City</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Regina Youth Club Basketball League (R=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Buffalo Narrows Friendship Centre</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Living Skies Indigenous Basketball Lea=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>North West Friendship Centre</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Living Skies Indigenous Basketball Lea=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Prince Albert Friendship Centre</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Living Skies Indigenous Basketball Lea=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Kikinahk (La Ronge) Friendship Centre</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Living Skies Indigenous Basketball Lea=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Saskatoon Friendship Centre</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Living Skies Indigenous Basketball Lea=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Battlefords Friendship Centre</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Living Skies Indigenous Basketball Lea=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Newo Yotina Friendship Centre</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Living Skies Indigenous Basketball Lea=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Qu'Appelle Valley Friendship Centre</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Living Skies Indigenous Basketball Lea=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Xcite Athletics</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Regina Raptors</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>306 Heat</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Melfort</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Stutter Steps Hoop Club</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Team FN</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Supernovas</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>LYB Rams</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Bucks</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Regina Youth Club Basketball League (R=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Regina Ballers</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Regina Youth Club Basketball League (R=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Île-à-la-Crosse Friendship Centre</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Living Skies Indigenous Basketball Lea=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>La Loche Friendship Centre</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Living Skies Indigenous Basketball Lea=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Yorkton Blue Jays</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Battleford Jr. Crusaders</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>YXE Elite</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Saskatchewan Sky</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>GT Thunder (Prince Albert)</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MJ Spartans</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Regina Swarm</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Prairie Fire Basketball</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BSI Club Championships (Basketball Sas=1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C60"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/research/provinces/SportsHub-Saskatchewan.xlsx
+++ b/docs/research/provinces/SportsHub-Saskatchewan.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Club Sizes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$Q$108</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$102</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$99</definedName>
@@ -65,11 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P108"/>
+  <dimension ref="A1:Q108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -454,6 +455,7 @@
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,6 +539,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Teams Counted</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1140,6 +1147,9 @@
           <t>Listed in BSI 2025/26 member registry as a Humboldt club; no independent web presence found — may be the rep arm alongside HMBA. Thin-evidence entry. | Type: club/rep program (listed as a current member org of Basketball Saskatchewan; only web presence found is that registry entry, which links mailto:BASKETBALLHUMBOLDT@GMAIL.COM). No website, Facebook, news coverage, or named principal found despite multiple searches — possibly the rep/club arm alongside HMBA in the same town (unconfirmed). Source: https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
+      <c r="Q10" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3215,6 +3225,9 @@
           <t>BSI member club; only public presence is Instagram (@306.heat.basketball, linked from BSI registry) | Type: club/rep program. Basketball Saskatchewan current-member registry entry links directly to this Instagram (@306.heat.basketball, display name '306 HEAT') — the club's only web presence found. Instagram bio/contact details not extractable (login-gated); no website, email, phone, or named principal found via news/registry searches. Sources: https://www.basketballsask.com/member-organizations/currentmembers ; https://www.instagram.com/306.heat.basketball/</t>
         </is>
       </c>
+      <c r="Q40" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3468,6 +3481,9 @@
           <t>BSI member club; registry contact email gottsela@hotmail.com</t>
         </is>
       </c>
+      <c r="Q44" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4073,6 +4089,9 @@
           <t>BSI member club; no contact info published in registry | Type: club (per PSO registry). ONLY evidence found: listed as "Queen City Black Caps (Regina)" under Clubs on the Basketball Saskatchewan current-members registry (https://www.basketballsask.com/member-organizations/currentmembers) with no hyperlink or contact attached. No website, social pages, news, or tournament listings found in extensive searching. Enrichment likely requires emailing Basketball Sask (basketball@basketballsask.com).</t>
         </is>
       </c>
+      <c r="Q54" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4130,6 +4149,9 @@
           <t>Separate BSI member from the club listed simply as 'Splash' (different registry contact)</t>
         </is>
       </c>
+      <c r="Q55" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4373,6 +4395,9 @@
           <t>BSI member club; website live but near-empty (title only) as of research date | Type: rep/club travel program. Basketball Sask member club (https://www.basketballsask.com/member-organizations/currentmembers). Phone+email extracted from site's embedded contact config (displayContactEmail/displayContactPhone) at https://www.reginaraptors.ca/. PLATFORM INTEL: website runs on Jersey Watch (org id 13708, Stripe Connect enabled) — not RAMP/TeamLinkt. Staff page exists but staffMembers list is empty (no coaches/officials published). Socials: facebook.com/profile.php?id=100094144893472, instagram.com/reginaraptors. Principal not publicly listed anywhere found.</t>
         </is>
       </c>
+      <c r="Q59" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5193,6 +5218,9 @@
           <t>Alternate phone 306-949-2483 (Yellow Pages) and 306-216-7603 (apparel). ~2000 sq ft own facility near downtown. On-site booking system (platform unidentified). BSI member</t>
         </is>
       </c>
+      <c r="Q74" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7479,6 +7507,9 @@
           <t>Program administered with Golden Ticket Sports (contact Jason Payne). Legion-sponsored ('Yorkton Legion Blue Jays'). Migrated RAMP → TeamLinkt = software-switch intel | Also listed as: Yorkton Blue Jays Basketball Club</t>
         </is>
       </c>
+      <c r="Q107" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7533,7 +7564,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P108"/>
+  <autoFilter ref="A1:Q108"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/research/provinces/SportsHub-Saskatchewan.xlsx
+++ b/docs/research/provinces/SportsHub-Saskatchewan.xlsx
@@ -441,7 +441,7 @@
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -471,77 +471,77 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Teams Counted</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Owner/Principal</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Programs</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Leagues</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>Teams Counted</t>
         </is>
       </c>
     </row>
@@ -556,57 +556,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Biggar</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>recreation@townofbiggar.com</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Erin Poitras — community coordinator (Town of Biggar recreation)</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site, town recreation dept)</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
@@ -623,57 +623,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Carrot River</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>crrb@sasktel.net</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Miranda Blaber — community coordinator</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
@@ -690,57 +690,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Christopher Lake</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>lwagner@srsd119.ca</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Lynnae Wagner — community coordinator</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
@@ -757,62 +757,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Cumberland House</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>aaronfosseneuve@nlsd113.ca</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Aaron Fosseneuve — community coordinator</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Northern community (Northern Lights School Division contact).</t>
         </is>
@@ -829,62 +829,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Dundurn</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>sndriedger@hotmail.com</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Stacey Driedger — community coordinator (per SKY Communities page; listing appears to date from the 2019-20 season, so may be stale)</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Coordinator contact not captured from the SKY communities page (Outlook Area cluster); Dundurn is in Saskatoon's commuter belt. | Type: community Jr. NBA program under SKY (Saskatchewan Youth Basketball), Outlook Area. Runs on TeamLinkt (competitive intel). Parent-org contact: skybasketball@sasktel.net, (306) 780-9264, 2205 Victoria Ave, Regina SK S4P 0S4 (league HQ). Sources: https://leagues.teamlinkt.com/skybasketball/Communities ; https://www.skybasketball.ca/skybasketball/ContactUs</t>
         </is>
@@ -901,57 +901,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Estevan</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>estevanclubbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>https://www.facebook.com/p/Estevan-Club-Basketball-61571698045768/</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Dustin Wilson — Director</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Rep club in 3rd season (2026), ~140 athletes: U11 boys &amp; girls, U13 boys &amp; girls, Gr 8 boys, U15 and U17 boys &amp; girls; draws players from Estevan plus Arcola, Stoughton, Carlyle and Weyburn</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>BSI-sanctioned spring club tournament circuit (2026)</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>https://www.discoverestevan.com/articles/estevan-club-basketball-sees-record-growth-in-2026-season</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Only rep club in the far southeast; effectively also serves Weyburn rep players. | Also listed as: Estevan Club Basketball</t>
         </is>
@@ -968,57 +968,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Hafford</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>jillb2@hotmail.com</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Jill Barnstable — community coordinator</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
@@ -1035,57 +1035,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Hudson Bay</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>april.danielle@nesd.ca</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Danielle April — community coordinator</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
@@ -1102,53 +1102,53 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Humboldt</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>basketballhumboldt@gmail.com</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>BSI Club Championships (Basketball Saskatchewan Provincials); BSI-sanctioned club tournament circuit (inferred from BSI club membership)</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>community nonprofit (club team)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Listed in BSI 2025/26 member registry as a Humboldt club; no independent web presence found — may be the rep arm alongside HMBA. Thin-evidence entry. | Type: club/rep program (listed as a current member org of Basketball Saskatchewan; only web presence found is that registry entry, which links mailto:BASKETBALLHUMBOLDT@GMAIL.COM). No website, Facebook, news coverage, or named principal found despite multiple searches — possibly the rep/club arm alongside HMBA in the same town (unconfirmed). Source: https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1162,62 +1162,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Humboldt</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>bhkusch@hotmail.com</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>https://www.facebook.com/people/Humboldt-Minor-Basketball-Association/</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Kerri Archibald — organizer/representative (title not published)</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Grades 1-6 basketball: Gr 1-2 co-ed at Humboldt Public School, Gr 3-4 boys &amp; girls at St. Augustine School, Gr 5-6 boys &amp; girls at HCI; Sunday-afternoon season Mar 2-May 11; $100 fee; 120+ athletes in inaugural 2024 season; hosts a Jr. NBA tournament</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>TeamLinkt</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>https://www.discoverhumboldt.com/articles/humboldt-minor-basketball-association-gearing-up-for-its-second-season</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Registration via QR codes in schools / TeamLinkt online. | Type: community minor basketball association. Programs Gr 1-6 (spring Sunday league, $100 fee) plus U13/U15/Open for Gr 7-12. Registers via TeamLinkt (competitive intel), link distributed through its Facebook page — no standalone website found. No email/phone/address published; Facebook page is the stated contact channel. No president/board names found in registry or news. Sources: https://www.discoverhumboldt.com/articles/humboldt-minor-basketball-association-gearing-up-for-its-second-season ; https://discoverhumboldt.com/articles/registration-open-for-senior-categories-of-humboldt-minor-basketball-association-spring-program ; https://discoverhumboldt.com/articles/humboldt-minor-basketball-hosts-weekend-tournament | Also listed as: Humboldt Minor Basketball Association</t>
         </is>
@@ -1234,62 +1234,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Indian Head</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>306-550-7645 (Josh Godlien) or 306-695-7420 (Doug Gheyssen)</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>dgheyssen@sasktel.net</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>https://www.ihactivities.ca</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Community basketball / Jr. NBA programming Gr 2 through Gr 5/6 (boys and girls groups), games at IH Elementary and IH High School</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>SportsEngine (ihactivities.ca town-wide sports hub); TeamLinkt for Jr. NBA registration via Basketball SK</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Small-town BSI member captured from registry sweep. | enriched 2026-07-18</t>
         </is>
@@ -1306,57 +1306,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Kelvington</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Kim.nicholls@horizonsd.ca</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Kim Nicholls — community coordinator</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
@@ -1373,62 +1373,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Kindersley</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>jessie_099@hotmail.com</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Jessica Secord — community coordinator</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>BSI member registry also lists a Kindersley club team based at Elizabeth Middle School — school-hosted, excluded from this census per school-team exclusion rule.</t>
         </is>
@@ -1445,57 +1445,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Langham</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>jennaharder@hotmail.com</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Jenna Harder — community coordinator</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
@@ -1512,57 +1512,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Luseland</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>dan@holmanfarminggroup.com</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Dan Holman — community coordinator</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
@@ -1579,57 +1579,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Martensville</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>(306) 683-5577</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>areddekopp@martensville.ca</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Angie Reddekopp — City of Martensville Recreation Program Supervisor (program lead)</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Mini Dunkers (K-Gr2), Spuds (Gr3-4), Mini (Gr5-6), Bantam (Gr7-8), Junior (Gr9-10), Senior (Gr11-12); U13 club team 'Martensville Thunder' (winter practices, spring tournaments); hosts annual January tournament</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Saskatoon Minor Basketball Association (SMBA) — community teams registered into SMBA programs; BSI-sanctioned spring club tournament circuit (Martensville Thunder U13); Saskatoon Minor Basketball Association (SMBA)</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>municipal recreation program / community (BSI member as 'Martensville Basketball')</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>https://martensvillemessenger.ca/basketball-season-underway-in-martensville/</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Run through the city recreation department rather than an independent association — a distinct GTM profile. | Also listed as: Martensville Basketball</t>
         </is>
@@ -1646,62 +1646,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Meadow Lake</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>alan.robin@nwsd.ca</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Alan Robins — coordinator grades 1-4; Jim Snodgrass — coordinator grades 5/6 (Jim.Snodgrass@nwsd.ca)</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball, split grades 1-4 and 5/6 programs</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>Coordinators are Northwest School Division staff; community program hosted through schools.</t>
         </is>
@@ -1718,62 +1718,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Melfort</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>penand00@gmail.com</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Penny Anderson — community coordinator</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Joint Melfort/Kinistino program.</t>
         </is>
@@ -1790,42 +1790,42 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Melville</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>mambasclubbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Club basketball (details not published)</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>BSI member club (Melville, near Yorkton); email suggests full name 'Mambas Club Basketball'; unrelated to Regina Mambas</t>
         </is>
@@ -1842,72 +1842,72 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Moose Jaw</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>1599 Main St N, Moose Jaw, SK S6J 1L5</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>306-693-5622</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>tanner@goldenticketsports.com</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>https://goldenticketsports.com/</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Tanner Brightman (Regina) and Chris King (Lloydminster) — co-founders</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Multi-sport private operator (basketball, volleyball, baseball, tennis): runs Moose Jaw Minor Basketball League (grades 2-8), Elite Development Program (ages 12-18), 200+ hours/yr of development camps (Christmas/Easter/summer), RCSD Basketball Academy (Regina) and Saskatoon Public Schools Basketball Academy via school-division partnerships; also operates Hoop Factory facility in Lloydminster</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Moose Jaw Minor Basketball League (Golden Ticket Sports)</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>multi-sport org (private)</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>LeagueApps (sportscentre.leagueapps.com and goldenticketsports.leagueapps.com)</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>https://goldenticketsports.com/</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>5-year agreement with City of Moose Jaw to operate the venue ($300K invested). Registry lists stephen@goldenticketbasketball.com as MJ Minor Basketball League contact. Alt phone 306-541-9112. LeagueApps user = competitive software intel</t>
         </is>
@@ -1924,72 +1924,72 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Moose Jaw</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Golden Ticket Sports Centre, 1599 Main St N, Moose Jaw, SK S6J 1L5 (corporate: 2362 McGregor Place, Regina)</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>306-693-5622</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>tanner@goldenticketsports.com</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>https://www.goldenticketsportscentre.com</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Tanner Brightman (Regina) &amp; Chris King (Lloydminster) — co-founders/owners of Golden Ticket Sports Inc.</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Operates Golden Ticket Sports Centre multi-sport facility (5-yr agreement with City of Moose Jaw, $300K investment); Moose Jaw Minor Basketball league Gr 2-8 (fall/winter sessions); Golden Ticket club teams (regional); boys/girls camps; academies; school-division training partnerships; CJBL U20 junior league (18+ — outside youth scope)</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Moose Jaw Minor Basketball League (Golden Ticket Sports) — operates</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>private multi-sport org</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>LeagueApps (sportscentre.leagueapps.com)</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>https://www.goldenticketsportscentre.com/</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Also runs Hoop Factory facility in Lloydminster (other region). BSI registry contacts: stephen@goldenticketsports.com (club), stephen@goldenticketbasketball.com (MJ Minor Basketball League). Also connected to Yorkton Blue Jays (Jason Payne uses @goldenticketsports.com email). Key LeagueApps account in SK.</t>
         </is>
@@ -2006,52 +2006,52 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Moose Jaw</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>mjballers18@gmail.com</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>https://www.facebook.com/groups/1728174240798337/</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Raman Mall, Founder/Head Coach</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Youth basketball program (Facebook group community)</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>BSI registry entry + Facebook group; distinct from 'little BALLERS' intro program. | Also listed as: Moose Jaw Ballers | enriched 2026-07-18</t>
         </is>
@@ -2068,42 +2068,42 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Moose Jaw</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>andrews.garry@gmail.com</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>BSI member club; registry contact Garry Andrews (role not stated); no independent web presence found</t>
         </is>
@@ -2120,57 +2120,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Moose Jaw</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>mjspartans17@gmail.com</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>https://www.facebook.com/p/Spartans-Club-Basketball-100063684334994/</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Ryan Boughen and Barry Seaborn — co-founders</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Club/rep basketball; plays spring club tournament circuit (hosted player raffle at Premier Prairie Classic Club Basketball Tournament); community fundraising (food bank donation)</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>BSI-sanctioned spring club tournament circuit (2026)</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>https://www.discovermoosejaw.com/articles/moose-jaw-spartans-basketball-club-donates-1000-to-local-food-bank</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>BSI member club</t>
         </is>
@@ -2187,57 +2187,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Moose Jaw</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>mjspartans17@gmail.com</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>https://www.facebook.com/100063684334994/</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Ryan Boughen &amp; Barry Seaborn — co-founders</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Rep club with teams in U13, U15, U17 divisions (7 teams entered own tournament in 2026); hosts annual Premier Prairie Classic tournament (57 teams from SK/AB, 90 games across four schools); community fundraising (food bank donations)</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>BSI-sanctioned spring club tournament circuit (2026)</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>https://www.discovermoosejaw.com/articles/moose-jaw-spartans-basketball-club-donates-1000-to-local-food-bank</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Premier Prairie Classic is a major stop on the provincial club circuit (Estevan, Yorkton Blue Jays teams attend).</t>
         </is>
@@ -2254,62 +2254,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK (multi-location program)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Moose Jaw</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>600 Saskatchewan St. W, Moose Jaw, SK (Saskatchewan Polytechnic); 920 11 Ave NW, Moose Jaw, SK (St. Michael School)</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>1-204-298-2925</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>info@littleballersbasketball.com</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>https://littleballersbasketball.com</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Chad Declaire — Owner (former U of R basketball standout)</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>Early-childhood intro basketball: Baby Ballers, Little Ballers, Mini Ballers divisions; launched Moose Jaw programming with 100+ signups for free awareness classes</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>private academy (intro program)</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>https://www.moosejawtoday.com/local-news/little-ballers-youth-basketball-program-coming-to-moose-jaw-8406570</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Multi-location private program (see locations page); Moose Jaw is the documented expansion site — check other SK locations during dedup. | enriched 2026-07-18</t>
         </is>
@@ -2326,42 +2326,42 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Moosomin</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>bdodds@hotmail.com</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>Club basketball (details not published)</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>BSI member club in small southeast-SK town; no independent web presence found</t>
         </is>
@@ -2378,62 +2378,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Nipawin</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>d.seckinger@nipawin.com</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Derek Seckinger — community coordinator</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Coordinator email is a Town of Nipawin address — likely municipally supported.</t>
         </is>
@@ -2450,67 +2450,67 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>North Battleford</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Programs hosted at North Battleford Central School</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>306-445-8216</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>nbimfc@sasktel.net</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>https://www.livingskiesbasketball.com/battlefordsfc</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Jackie Kennedy — Executive Director, Battlefords Indian &amp; Métis Friendship Centre</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>LSIBL junior girls and junior boys (ages 15-17) weekly sessions; senior girls/boys division planned; Indigenous youth focus with cultural/social workshops</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Living Skies Indigenous Basketball League (LSIBL)</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>community nonprofit (friendship centre-hosted program)</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>https://www.livingskiesbasketball.com/battlefordsfc</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>This is the main structured youth club basketball presence found in North Battleford — no independent minor basketball association was found for the city. | Community/Indigenous program (Junior &amp; Senior Girls/Boys divisions) run by the Friendship Centre within the Living Skies Indigenous Basketball League (LSIBL, operated by Aboriginal Friendship Centres of Saskatchewan). Practices at North Battleford Central School. Centre board President: Becky Trotchie. League-level contact: pcrozo@afcs.ca, (306) 955-0762 (livingskiesbasketball.com/contact). Address/phone/email/ED sourced from https://afcs.ca/centre/battleford-indian-metis-friendship-centre/ (also 306-441-2689 cell, fax 306-445-6863). Program page itself lists no direct contacts. Type: community association program.</t>
         </is>
@@ -2527,62 +2527,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>North Battleford</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>l.sander@hotmail.com</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Eric &amp; Loralee Cawood — community coordinators</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Jr. NBA grassroots youth basketball program for the Battlefords, run under SKY Basketball / Saskatchewan Youth Basketball</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>community program (volunteer-coordinated SKY community)</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY Basketball platform)</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Coordinator contact published on the SKY communities page.</t>
         </is>
@@ -2599,72 +2599,72 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>North Battleford</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>960 - 103rd Street, North Battleford, SK S9A 1K2</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>306-445-8216</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>nbimfc@sasktel.net</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>https://www.livingskiesbasketball.com/battlefordsfc</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Jackie Kennedy — Executive Director (Battlefords Indian &amp; Métis Friendship Centre)</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Four competitive Indigenous youth teams: Junior Girls, Junior Boys, Senior Girls, Senior Boys; junior practices Wednesday evenings at North Battleford Central School</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Living Skies Indigenous Basketball League (LSIBL)</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>community org (Friendship Centre program)</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>TeamLinkt (LSIBL registration)</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>https://www.livingskiesbasketball.com/battlefordsfc</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>LSIBL central coordinator Paige Crozon (306-955-0762, pcrozon@afcs.ca) is the league-level contact. | Type: Indigenous community program (friendship-centre chapter of the Living Skies Indigenous Basketball League). Four teams (Jr/Sr Girls &amp; Boys); junior practices at North Battleford Central School Wednesdays. Player registration via TeamLinkt (competitive intel: LSIBL runs on TeamLinkt); LSIBL page directs contact through the league's main contact form. Address/phone/email/ED are the parent Friendship Centre's (program-specific contact not published). Sources: https://www.livingskiesbasketball.com/battlefordsfc ; https://afcs.ca/centre/battleford-indian-metis-friendship-centre/ ; https://www.yellowpages.ca/bus/Saskatchewan/North-Battleford/Battleford-s-Indian-Metis-Friendship-Centre/162290.html</t>
         </is>
@@ -2681,62 +2681,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Outlook</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>amber.thompson@sunwestsd.ca</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Amber Thompson — community coordinator (per SKY Communities page; listing appears to date from the 2019-20 season, so may be stale)</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program (SKY 'Outlook Area' cluster: Outlook, Rosetown, Dundurn, Beechy, Central Butte, Loreburn)</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Coordinator name/contact not captured from the SKY communities page for this cluster; region-boundary note: Outlook area sits between the Saskatoon and Regina/south census regions — dedupe against the south run. | Type: community Jr. NBA program under SKY (Saskatchewan Youth Basketball), Outlook Area hub of the league. Runs on TeamLinkt (competitive intel). Parent-org contact: skybasketball@sasktel.net, (306) 780-9264, 2205 Victoria Ave, Regina SK S4P 0S4 (Basketball Sask/Sask Sport building — league HQ, not a local program address). Sources: https://leagues.teamlinkt.com/skybasketball/Communities ; https://www.skybasketball.ca/skybasketball/ContactUs</t>
         </is>
@@ -2753,57 +2753,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Paradise Hill</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>dimples1973fink@gmail.com</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Leanne Fink — community coordinator</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
@@ -2820,57 +2820,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Porcupine Plain</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>boyle.Jocelyn@nesd.ca</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Jocelyn Boyle — community coordinator</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
@@ -2887,57 +2887,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Prince Albert</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>thunderbasketball.sk@gmail.com</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>https://www.facebook.com/thunderbball306/</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Adie Schenk — co-founder and coach (U17 girls)</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Club teams U11, U13, U15, U17 boys and girls; skill development training; winter SMBA season (90+ athletes yr 2) and spring session (130+ registered); hosts the PA Thunder Basketball Tournament; 'super-inclusive' mandate</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>Saskatoon Minor Basketball Association (SMBA); BSI Club Championships (Basketball Saskatchewan Provincials); BSI-sanctioned spring club tournament circuit (2026); Saskatchewan club tournament circuit</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>community nonprofit (inclusive rep club)</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>https://panow.com/2022/04/07/new-basketball-club-adopts-its-name-from-late-local-champion/</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>Founded 2022; named in honour of the late Victor Thunderchild, Carlton Comprehensive teacher. Instagram @thunderbball306.</t>
         </is>
@@ -2954,72 +2954,72 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Prince Albert</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>RR 1 Prince Albert, SK S6V 5P8</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>306-960-0430</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>pacommunitybasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>https://pacommunitybasketball.com</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Jim Guidinger, Executive Director</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>Ages 5+: Jr NBA (Gr 1-3, 8-week Sunday sessions), PACBA recreational house league, and Lakers competitive club teams (11U/Gr3-5 boys, Gr3-4 and Gr5-6 girls, 13U boys, 15U boys Gold/Silver); fees ~$150-450</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Prince Albert Community Basketball Association (PACBA) Winter League — self-operated; SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA); BSI Club Championships / provincial club tournament circuit (Lakers teams)</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>RAMP Interactive (CMS + registration)</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>http://pacommunitybasketball.com</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>RAMP customer — competitive intel. Board names not published. | enriched 2026-07-18</t>
         </is>
@@ -3036,72 +3036,72 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Prince Albert</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>RR 1 Prince Albert, SK S6V 5P8</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>306-960-0430</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>pacommunitybasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>https://pacommunitybasketball.com/</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Jim Guidinger, Executive Director</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>Instruction and teams ages 5+; winter community league; 'Lakers' spring club teams: 11U (Gr 3-5 boys, 2015-17), 13U boys (2013-14), 15U boys Gold &amp; Silver (2011-12), high-school boys, girls Gr 3/4 and Gr 5/6; Apr-Jun season, 2-4 regional one-day tournaments, fees $150-$450; 2026 tryouts early-mid February</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Prince Albert Community Basketball Association (PACBA) Winter League; BSI-sanctioned spring club tournament circuit (2026)</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>RAMP InterActive</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>https://pacommunitybasketball.com/content/lakers</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>PACBA operates both the mapped PACBA Winter League and the Lakers club program. Listed on City of Prince Albert sports directory. | enriched 2026-07-18</t>
         </is>
@@ -3118,57 +3118,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Rapid View</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>mc_nolin@yahoo.ca</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Carmen Nolin — community coordinator</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
@@ -3185,48 +3185,48 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>https://www.instagram.com/306.heat.basketball/</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>BSI member club; only public presence is Instagram (@306.heat.basketball, linked from BSI registry) | Type: club/rep program. Basketball Saskatchewan current-member registry entry links directly to this Instagram (@306.heat.basketball, display name '306 HEAT') — the club's only web presence found. Instagram bio/contact details not extractable (login-gated); no website, email, phone, or named principal found via news/registry searches. Sources: https://www.basketballsask.com/member-organizations/currentmembers ; https://www.instagram.com/306.heat.basketball/</t>
         </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -3240,67 +3240,67 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>2250 Lindsay St, Regina, SK S4N 3C3</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>306-352-3930</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>info@alritchie.org</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>https://www.alritchie.org/</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Denis Simard, Executive Director</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>Neighbourhood community association (registered charity est. 1987) offering a youth basketball program among social/recreation programs</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>multi-sport / community nonprofit organization</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Amilia (app.amilia.com/store/en/alritchie)</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>https://www.alritchie.org/</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>Youth basketball program page indexed in search but URL returned 404 on direct fetch — program details may have moved; main org details verified. Likely feeds the RCBA community system but affiliation not published | enriched 2026-07-18</t>
         </is>
@@ -3317,47 +3317,47 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>info@reginaballersbasketball.com</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>https://reginaballersbasketball.com</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Rep/club teams by birth-year cohorts (2012, 2013, 2014); Canada Basketball Verified club (background checks, Safe Sport)</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>https://reginaballersbasketball.com/</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>BSI member club; league play not published on site.</t>
         </is>
@@ -3374,52 +3374,52 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>info@reginaballersbasketball.com</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>https://reginaballersbasketball.com/</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>Rep/club teams organized by birth year (2012, 2013, 2014 team contact emails published); Canada Basketball Verified club</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>Regina Youth Club Basketball League (RYCBL); BSI Club Championships (Basketball Saskatchewan Provincials)</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>https://reginaballersbasketball.com/</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>Per-age-group team emails: 2012Teams@/2013Teams@/2014Teams@reginaballersbasketball.com</t>
         </is>
@@ -3436,53 +3436,53 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>gottsela@hotmail.com</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Club/rep teams, grades ~6-8 evidenced</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>Regina Youth Club Basketball League (RYCBL)</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>BSI member club; registry contact email gottsela@hotmail.com</t>
         </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -3496,37 +3496,37 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>BSI member club, Regina; no contact info or web presence found. Name suggests University of Regina Cougars affiliation but unverified | Type: club/rep program (listed plain-text, no hyperlink, on Basketball Saskatchewan's current-member registry). No website, social page, registration page, news coverage, or named principal found after multiple targeted searches (incl. U of R Cougars affiliation angle, RYCBL and RCBA league sites, Exposure). Name may relate to University of Regina Cougars youth pipeline but this is unverified. Source: https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
@@ -3543,32 +3543,32 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>club (unspecified)</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>Separate BSI registry line from Cougar Selects — likely a team of the same program; keep for dedup review.</t>
         </is>
@@ -3585,57 +3585,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Scott Collegiate, North Central Regina (program venue)</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>firstnationsbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>https://sites.google.com/view/fn-basketball/home</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Daniel Stonechild — Founder (educator, basketball coach)</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Indigenous youth program: basketball camps, U18 club teams (Team FN Gold, Team FN Silver), prep team; integrates Cree language and Indigenous teachings</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>community nonprofit (Indigenous youth club)</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>https://sites.google.com/view/fn-basketball/home</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>Natural fit/likely participant in LSIBL circuit but league play not published — do not assume.</t>
         </is>
@@ -3652,52 +3652,52 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>firstnationsbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>https://www.instagram.com/firstnationsbasketball/</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Daniel Stonechild — founder (teacher at Scott Collegiate, Regina)</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>Indigenous-focused basketball training + life lessons through cultural teachings; camps and sessions for Grade 5 through high school; started 2021; planning on-reserve camps and U19 Indigenous Games team</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>private academy (Indigenous-focused training organization)</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>https://www.620ckrm.com/2025/06/12/regina-program-combines-basketball-and-life-lessons-for-youth/</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>BSI member club (website linked from registry). Natural fit/overlap with Living Skies Indigenous Basketball League but no published team-league mapping found | Type: Indigenous community/nonprofit club + academy (est. 2021). Founder Daniel Stonechild (teacher at Scott Collegiate, Regina) per 620 CKRM / SaskToday coverage June 2025 (https://www.620ckrm.com/2025/06/12/regina-program-combines-basketball-and-life-lessons-for-youth/); coach Terreign Blind also named. Programs based at Scott Collegiate, North Central Regina (venue, not verified registered office — address left blank). Email + founder bio from official Google Sites page (linked from Basketball Sask member registry). Club teams: Team FN Gold, Team FN Silver (U18) + prep team. Socials: instagram.com/firstnationsbasketball, Facebook 'FN Basketball'. No registration platform identified.</t>
         </is>
@@ -3714,72 +3714,72 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>661 Solomon Crescent, Regina, SK S4N 6H9</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>306-993-4570</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>info@hooplifebasketball.com</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>https://www.hooplifebasketball.com/regina/home</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Andrew Gottselig — founder &amp; CEO; Habib Habib — co-founder &amp; Executive Director</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>For-profit academy, ages 4-17: HoopLife League (Gr 1-8, Oct-Apr), Spring League (Gr 1-8, Apr-Jun), Young Stars (ages 4-6), Elevate (14-17), girls-only sessions, 1-on-1 coaching, camps (summer/Easter/Feb break/Christmas), pro-level clinics; expanded to Saskatoon 2024; mini-camps across rural SK</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>HoopLife League (Regina, fall/winter); HoopLife Spring League (Regina); HoopLife League (Regina, fall/winter) — operates; HoopLife Spring League (Regina) — operates</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>Citrus Camps (register.citruscamps.com)</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>https://www.hooplifebasketball.com/regina/home</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>Official youth development partner of CEBL Saskatchewan Rattlers (rebranded Saskatoon Mamba 2026). Biggest private youth basketball operator in Regina — key GTM target/competitor-adjacent org</t>
         </is>
@@ -3796,67 +3796,67 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>3450 Westgate Ave, Regina, SK S4S 1B5</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>306-530-6770</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>masterpiececamps@gmail.com</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>https://www.masterpiececamps.com</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Geoff Glasspell ("Coach Geoff") — Founder; U of R Cougars alum 1998-2002, teacher/AD at Regina Christian School</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>Camps and training: Gr 1-4 Training Ground (Sept-Nov), summer camps, seasonal skills programs</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>private academy (camps/training)</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>Wix bookings (service-page registration on own site)</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>https://www.masterpiececamps.com/about</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>Listed under Training &amp; Other Programs in BSI registry. | Private academy/camps operation: co-ed camps Gr 1-12, mini-leagues, training-ground programs; faith/character-values branding. Site About page names 'Coach Geoff' as founder (U of Regina Cougars alum 1998-2002, teacher/AD at Regina Christian School); corporate entity Glasspell Leadership Corp shown in site footer; ZoomInfo corroborates Geoffrey Glasspell as President (https://www.zoominfo.com/p/Geoffrey-Glasspell/1164960287). COMPETITIVE INTEL: camp registration runs on Citrus Camps platform (register.citruscamps.com). Sources: https://www.masterpiececamps.com, https://www.masterpiececamps.com/about. Basketball Sask member (Training Programs). Type: private academy.</t>
         </is>
@@ -3873,57 +3873,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>jeremy.sundeen@gmail.com</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>https://misfitsbasketball.com</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Bree Burgess &amp; Leah Levy (co-founders, former U of R Cougars players); Jeremy Sundeen (co-founder, BSI VP of Coaches Development); Jared Woloshyn (co-founder)</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>Girls club teams (Grade 5/6 evidenced)</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>Regina Youth Club Basketball League (RYCBL)</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>BSI member club; registry contact Jeremy Sundeen (role not stated)</t>
         </is>
@@ -3940,47 +3940,47 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>mericbauda@gmail.com</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>https://www.instagram.com/yqr.novaelite/</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>club (unspecified)</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>BSI registry entry; Instagram (@yqr.novaelite) and YouTube channel exist. | Also listed as: Nova Elite</t>
         </is>
@@ -3997,42 +3997,42 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>prairiedreambasketball@gmail.com</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>BSI member club, Regina</t>
         </is>
@@ -4049,48 +4049,48 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>Club/rep teams (Boys Grade 7/8 evidenced)</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>Regina Youth Club Basketball League (RYCBL)</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>BSI member club; no contact info published in registry | Type: club (per PSO registry). ONLY evidence found: listed as "Queen City Black Caps (Regina)" under Clubs on the Basketball Saskatchewan current-members registry (https://www.basketballsask.com/member-organizations/currentmembers) with no hyperlink or contact attached. No website, social pages, news, or tournament listings found in extensive searching. Enrichment likely requires emailing Basketball Sask (basketball@basketballsask.com).</t>
         </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -4104,53 +4104,53 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>queencitysplash@gmail.com</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>Club/rep teams (Boys Grade 7/8 evidenced)</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>Regina Youth Club Basketball League (RYCBL)</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>Separate BSI member from the club listed simply as 'Splash' (different registry contact)</t>
         </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -4164,47 +4164,47 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>cdandresfamily@gmail.com</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>Club/rep teams (Boys Grade 7/8 evidenced)</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>Regina Youth Club Basketball League (RYCBL)</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>BSI member club</t>
         </is>
@@ -4221,62 +4221,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>306-584-3222</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>https://www.rcba.ca</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>Brett Fisher — President; Landon Barr — Executive Director; Tess Rispens-Sisco — Assistant Executive Director</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>Community house league ages 5-18 (Jr. Cougars K, Gr 1-2, Gr 3, Gr 4, Gr 5/6, Gr 7/8, High School), All-Stars program, Player Skills Camps, New Player Clinics, Basketball Around the City</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>Regina Community Basketball Association (RCBA) — operates its own house league</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>TeamLinkt (website + registration); SkillShark (athlete evaluations — case study: 1,200 kids registered in 10 minutes)</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>https://www.rcba.ca/rcba/</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>Also one of the mapped leagues for this province. Largest community basketball org in Regina.</t>
         </is>
@@ -4293,42 +4293,42 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>reginamambasclub@gmail.com</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>Youth club (players ~12-13 as of 2019 CBC story); started as a Grade 5 group</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>https://www.cbc.ca/news/canada/saskatchewan/raptors-win-young-basketball-players-regina-1.5182380</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>Distinct from Melville Mambas (different BSI registry entry and email).</t>
         </is>
@@ -4345,58 +4345,58 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>306-596-1470</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>reginaraptors@gmail.com</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>https://www.reginaraptors.ca/</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>https://www.reginaraptors.ca/</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>BSI member club; website live but near-empty (title only) as of research date | Type: rep/club travel program. Basketball Sask member club (https://www.basketballsask.com/member-organizations/currentmembers). Phone+email extracted from site's embedded contact config (displayContactEmail/displayContactPhone) at https://www.reginaraptors.ca/. PLATFORM INTEL: website runs on Jersey Watch (org id 13708, Stripe Connect enabled) — not RAMP/TeamLinkt. Staff page exists but staffMembers list is empty (no coaches/officials published). Socials: facebook.com/profile.php?id=100094144893472, instagram.com/reginaraptors. Principal not publicly listed anywhere found.</t>
         </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -4410,37 +4410,37 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>BSI member club, Regina; no contact info or web presence found | Type: club (per PSO registry). ONLY evidence found: listed as "Reining 3's (Regina)" under Clubs on the Basketball Saskatchewan current-members registry (https://www.basketballsask.com/member-organizations/currentmembers) with no hyperlink or contact attached. Extensive web/social searches (Instagram, Facebook, news, league sites) returned no independent web presence. Enrichment likely requires emailing Basketball Sask (basketball@basketballsask.com).</t>
         </is>
@@ -4457,47 +4457,47 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK (city per BSI grouping; base uncertain)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>kev@riseabovebasketball.ca</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>https://riseabovebasketballacademy.ca</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>Club basketball 9U-17U/High School divisions; teams travel to Edmonton, Calgary, Dawson Creek, Peace River, Fort St. John tournaments</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>private academy/club</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>https://riseabovebasketballacademy.ca/club-teams/</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>BSI registry lists it among Regina clubs, but academy Facebook handle (riseabovebasketballacademygp) and Peace-Country travel pattern suggest possible Grande Prairie AB linkage; website under construction. Verify base city before outreach.</t>
         </is>
@@ -4514,37 +4514,37 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>k_bellefleur@hotmail.com</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>club (unspecified)</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>BSI registry entry only.</t>
         </is>
@@ -4561,42 +4561,42 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>saskskybasketball@gmail.com</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>BSI member club. Distinct organization from SKY Basketball / Saskatchewan Youth Basketball (the provincial Jr. NBA program, already mapped as a league)</t>
         </is>
@@ -4613,42 +4613,42 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>k_bellefleur@hotmail.com</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>Listed as current BSI (Basketball Saskatchewan) member club, Regina; no independent web presence found</t>
         </is>
@@ -4665,47 +4665,47 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>200-235 12th Ave E, Regina, SK S4N 6B3</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>https://www.shoot360.com/regina</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>Immersive tech-driven basketball training (in-person coaching + digital gamification); facility opening 2026 — programs/hours listed as coming soon</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>private academy (franchise training facility)</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>https://www.shoot360.com/regina</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>US-based Shoot 360 franchise system; local operator not disclosed. Not yet a BSI member. Pre-launch as of July 2026 | Type: private academy — tech-driven training franchise (Shoot 360, founded by Craig Moody; corporate HQ USA). Regina facility NOT YET OPEN — anticipated 2026; site lists phone/email/hours as 'COMING SOON' (https://www.shoot360.com/regina). Local franchisee/owner not yet publicly disclosed (searched franchise press, PR Newswire, LinkedIn, local media — other Canadian locations e.g. Oakville name local owners, Regina does not). Re-check closer to opening; also NOT on Basketball Sask member registry as of this census.</t>
         </is>
@@ -4722,57 +4722,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>(306)-527-9241</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>homecourtbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>https://www.soldiersbasketball.org</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>"Moe" — Founder (surname not published on site)</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>Training academy 25+ years: skill sessions, player development, youth league play combining gameplay with structured training; Soldiers Academy sessions run at SASKHOMECOURT facility</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>https://www.soldiersbasketball.org/about</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>BSI registry links to saskhomecourt.com/soldiers — operates out of SaskHomeCourt facility. | Private academy + youth league, 25+ years operating; founder quoted on About page only as 'Moe, Founder' (https://www.soldiersbasketball.org/about) — full name not found, do not guess. Own site has contact form only, no address/phone/email; socials @soldiersbasketball574 (IG/FB). Basketball Sask member registry points Soldiers Academy registration to Sask HomeCourt: https://www.saskhomecourt.com/soldiers, which lists homecourtbasketball@gmail.com / (306) 527-9241 — those belong to Saskatchewan Home Court Basketball Inc. (registration partner, runs on TeamLinkt: app.teamlinkt.com/register/find/homecourtbasketballsummerleague), not confirmed as Soldiers' own line. Type: private academy. | enriched 2026-07-18</t>
         </is>
@@ -4789,57 +4789,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>306-527-9241</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>homecourtbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>https://www.saskhomecourt.com/soldiers</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>Academy skill-development sessions, private training, own summer league combining gameplay with structured training; funding applications offered for participants</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>PayPal checkout on SaskHomecourt site (registration platform otherwise unidentified)</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>https://www.saskhomecourt.com/soldiers</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>Operated under SaskHomecourt umbrella; BSI member. Instagram @soldiersacademy_ shows U16 teams. soldiersbasketball.org in searches is a Silicon Valley namesake — do not conflate</t>
         </is>
@@ -4856,42 +4856,42 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>m.stefaniuk@sasktel.net</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>BSI member club, Regina; listed separately from Queen City Splash (different contact email)</t>
         </is>
@@ -4908,37 +4908,37 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>m.stefaniuk@sasktel.net</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>club (unspecified)</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>Separate BSI registry line from Queen City Splash; possible duplicate — flag for dedup.</t>
         </is>
@@ -4955,47 +4955,47 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>306-530-5373</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>sasktriplethreat@gmail.com</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>BSI member club, Regina; no independent web presence found (Toronto Triple Threat and US namesakes are unrelated) | enriched 2026-07-18</t>
         </is>
@@ -5012,42 +5012,42 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>ral751@mail.usask.ca</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>BSI member club, Regina; no independent web presence found</t>
         </is>
@@ -5064,37 +5064,37 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>ral751@mail.usask.ca</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>club (unspecified)</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>BSI registry entry only.</t>
         </is>
@@ -5111,37 +5111,37 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>Club/rep basketball (details not published)</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>club (unspecified)</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>BSI registry entry only; no public web presence found (do not confuse with Whitehorse or US Wolfpack clubs). | Also listed as: Wolfpack Basketball</t>
         </is>
@@ -5158,68 +5158,68 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>Regina</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Bay #2, 1422 Elliott Street, Regina, SK S4N 3G5</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>306-501-3761</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>info.xciteathletics@gmail.com</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>https://xciteathletics.com/</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>Frankie L. Parris — CEO/owner</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>Private training academy since 2010: 1-on-1 and small-group training, Xcite Academy skill development, summer travel teams, community skill camps; youth ages 6-17</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>https://xciteathletics.com/</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>Alternate phone 306-949-2483 (Yellow Pages) and 306-216-7603 (apparel). ~2000 sq ft own facility near downtown. On-site booking system (platform unidentified). BSI member</t>
         </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -5233,62 +5233,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>Rosetown</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>jkatwhite@gmail.com</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>Judy White — community coordinator (per SKY Communities page; listing appears to date from the 2019-20 season, so may be stale)</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>Coordinator contact not captured from the SKY communities page (Outlook Area cluster). | Type: community Jr. NBA program under SKY (Saskatchewan Youth Basketball), Outlook Area. Runs on TeamLinkt (competitive intel). Parent-org contact: skybasketball@sasktel.net, (306) 780-9264, 2205 Victoria Ave, Regina SK S4P 0S4 (league HQ). Sources: https://leagues.teamlinkt.com/skybasketball/Communities ; https://www.skybasketball.ca/skybasketball/ContactUs</t>
         </is>
@@ -5305,57 +5305,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>Rosthern</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>Candicebihari@gmail.com</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>Candice Bihari — community coordinator</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
@@ -5372,62 +5372,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>Sandy Bay</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>atraxel@yahoo.com</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>Allen Traxel — community coordinator</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>Northern community.</t>
         </is>
@@ -5444,32 +5444,32 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK (placement uncertain)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>Saskatchewan (regional — base city not published)</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>club (unspecified)</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>BSI registry lists as 'Regional' with no contact; could belong to another region's census — include for dedup, verify before outreach.</t>
         </is>
@@ -5486,72 +5486,72 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>2813 20th (St), Saskatoon, SK (as published on site)</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>(306) 321-6777</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>sean.tsn@gmail.com</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>https://saskatoonbasketball.com</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>Sean Tyson — Technical Director (primary contact)</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>Elite boys development U11-U18 year-round (fall + winter programs); summer and skill-specific camps for ages 10-21; academy arm offers recruiting-service referrals and athletic-performance training; gear donation program</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>BSI Club Championships / BSI-sanctioned club tournament circuit; BSI Club Championships (Basketball Saskatchewan Provincials); BSI-sanctioned spring club tournament circuit (2026)</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>community nonprofit with private-academy arm</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>Squarespace site with built-in store/registration</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>https://saskatoonbasketball.com/what-we-do</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>Non-profit; BSI member club. Coaching staff advertised as youth-to-NBA experience. Online registration through own website portal (platform not named).</t>
         </is>
@@ -5568,67 +5568,67 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Saskatchewan Polytechnic, 1130 Idylwyld Dr N, Saskatoon, SK S7K 3R5</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>(306) 912-7072</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>saskatoon@hooplifebasketball.com</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>https://www.hooplifebasketball.com/saskatoon/home</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>Andrew Gottselig — founder &amp; CEO; Habib Habib — co-founder &amp; president (HoopLife Basketball Inc., Regina HQ)</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>Training 5 days/week for ages 4-17: 1-hour skill sessions (beginner/advanced), Young Stars (ages 4-6), girls-only sessions, open gym, seasonal camps (February break, Easter, Summer, November break, Christmas), pro-level clinics</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>private academy (branch of Regina-HQ HoopLife Basketball Inc.)</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>Citrus Camps (register.citruscamps.com)</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>https://www.hooplifebasketball.com/saskatoon/sessions/basketball-training</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>Expanded from Regina to Saskatoon in 2024 (Global News). HoopLife League (fall/winter) and HoopLife Spring League run in Regina — mapped separately; Saskatoon operation is training/camps so far. Company founded 2016.</t>
         </is>
@@ -5645,52 +5645,52 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>houndsvillehoops@gmail.com</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>https://www.instagram.com/houndsvillehoops/</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>High-level basketball coaching and elite training; 'Refining Basketball' ages 10-12; 'Levelling Up Basketball' ages 13+; community programming delivered in partnership with Stonebridge Community Association</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>BSI Club Championships (Basketball Saskatchewan Provincials)</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>private academy (player development / training)</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>Listed as a Saskatoon club in the BSI 2025/26 member registry; strongest presence is training programming in the Stonebridge neighbourhood. | Type: private training program/club. Email from mailto link on Basketball Saskatchewan current-members registry entry "Houndsville Hoops (Saskatoon)" (https://www.basketballsask.com/member-organizations/currentmembers). No website — Instagram-only presence (https://www.instagram.com/houndsvillehoops/). Partners with Stonebridge Community Association for neighbourhood training (Facebook post Mar 2025: https://www.facebook.com/stonebridgeyxe/posts/1120786306758055/), registration handled through ourstonebridge.ca portal. No principal named in any source found.</t>
         </is>
@@ -5707,52 +5707,52 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>https://www.facebook.com/onelovebasketball/</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>Mike Tanton — Co-Founder</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>Youth encouragement/development through basketball; delivery partner for the Living Skies Indigenous Basketball League alongside AFCS friendship centres</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>Living Skies Indigenous Basketball League (LSIBL); Living Skies Indigenous Basketball League (LSIBL) — co-operator</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>community nonprofit (youth development through basketball)</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>https://www.facebook.com/onelovebasketball/</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>Named as a supporting/delivery organization on LSIBL and SIMFC pages. | Type: nonprofit community basketball organization (founded 2016 by brothers Mike Tanton and Mason Medynski). Co-developed the Living Skies Indigenous Basketball League (2019/2021 launch) with the Aboriginal Friendship Centres of Saskatchewan; Tanton is also LSIBL co-founder (LSIBL uses TeamLinkt — competitive intel). Mason Medynski = second co-founder. No email/phone/address published; presence is Facebook + Instagram @one.love.basketball.inc. Saskatchewan ISC corporate registry is not freely searchable online, so incorporation record not retrieved. Sources: https://www.sasksport.ca/news/celebrating-indigenous-athletes-campaign-features-mike-tanton/ ; https://www.mbcradio.com/2021/09/new-indigenous-youth-basketball-league-to-start-in-october ; https://www.basketball.ca/news/living-skies-indigenous-basketball-leagues-becomes-the-latest-canada-basketball-unified-partner ; https://www.facebook.com/onelovebasketball/</t>
         </is>
@@ -5769,67 +5769,67 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Unit 10 - 147 Olson Lane West, Saskatoon, SK S7V 0L1</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>info@myrosewood.ca</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>https://www.myrosewood.ca/basketball.html</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>Courtney Thornhill — President</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>SMBA community-league basketball grades 1-12, boys and girls: Dunkaroos (Gr 1/2), Spuds (Gr 3/4), Minis (Gr 5/6), Bantam (Gr 7/8), Junior (Gr 9/10), Senior (Gr 11/12); season Oct-Mar</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>Saskatoon Minor Basketball Association (SMBA)</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>community nonprofit (multi-sport community association)</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>TeamLinkt</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>https://www.myrosewood.ca/basketball.html</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>One of many Saskatoon community associations fielding SMBA teams (SMBA works with community associations city-wide; only associations with direct evidence are listed in this census). Contact via Rosewood Basketball Coordinator email on page. | Type: community association youth program (teams play in Saskatoon Minor Basketball Association). Registration via TeamLinkt through SMBA (competitive intel: TeamLinkt). Basketball Coordinator per club board page: Ivan Gandzalas; SMBA's community-contacts page lists Rosewood basketball contact as Jerry Schuler (schulerjerry@gmail.com) — vintages differ, both documented. City of Saskatoon 2025 CA contact list names Erin Bentley (Program Coordinator) as association contact, email info@myrosewood.ca. Club basketball page's obfuscated emails decode to SMBA's (smba4712@gmail.com, saskatoonminorbasketball@gmail.com). Sources: https://www.myrosewood.ca/basketball.html ; https://www.myrosewood.ca/board.html ; https://smbayxe.ca/smba/CommunityBasketballContacts ; https://www.saskatoon.ca/sites/default/files/CA%20Contact%20List%20-%20Website%202025.pdf</t>
         </is>
@@ -5846,62 +5846,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>(306) 527-9241</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>homecourtbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>https://www.saskhomecourt.com/</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>Summer League (Season 6, June 21-Aug 20): grades 4-12 plus post-grad U21 division, A &amp; B skill divisions, $400+tax ($200 post-grad), weeknight games + practices; private training; Soldiers Academy. Venues: U of S PAC &amp; Education Gym, École Canadienne-Française, Martensville Athletic Pavilion</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>SaskHomeCourt Summer League (own league)</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>private academy / league operator</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>TeamLinkt (app.teamlinkt.com)</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>https://www.saskhomecourt.com/summerleague</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>Also runs sessions in Martensville via the Athletic Pavilion. Social: @saskhomecourtbasketball. | Type: private academy/training org + league operator. Legal name per registration page: 'Saskatchewan Home Court Basketball Inc.' Phone/email from https://www.saskhomecourt.com/contact. Runs SHC Summer League season 6 (Jun–Aug; venues: Martensville + University of Saskatchewan, Saskatoon — confirms Saskatoon base) and ALSO operates 'Soldiers Basketball Academy (Regina)' (saskhomecourt.com/soldiers, listed separately on Basketball Sask registry) — so footprint spans both cities. Site says family-run ('core to the family's values') but publishes no individual names; principal unknown. PLATFORM INTEL: registration on TeamLinkt (https://app.teamlinkt.com/register/find/homecourtbasketballsummerleague?cid=69298); website on Squarespace. Basketball Sask affiliate. IGs: @saskhomecourtbasketball, @shcleague.</t>
         </is>
@@ -5918,62 +5918,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>+1 639-597-3571</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>saskhoopselite@gmail.com</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>https://saskhoops.ca/</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>Kevin, Sergei and Vince Cabural — co-founders (brothers)</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>Training camps (since Dec 2018) plus five competitive teams for youth up to age 17; ~180 kids at peak (2023); teams competed across Saskatchewan and Alberta in 2024</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>BSI Club Championships (Basketball Saskatchewan Provincials); BSI-sanctioned spring club tournament circuit (2026); BSI-sanctioned club tournament circuit (Saskatchewan); Alberta club tournaments (teams competed across SK and AB in 2024)</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>private academy / club</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>https://www.cbc.ca/news/canada/saskatchewan/brothers-from-the-philippines-proud-basketball-club-grows-1.7295744</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>Founded by Filipino-Canadian brothers, originally to serve Saskatoon's Filipino community, now open to all backgrounds; became SaskHoops Elite in 2022. BSI member club. CBC News profile July 2024.</t>
         </is>
@@ -5990,72 +5990,72 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>168 Wall St, Saskatoon, SK S7K 1N4</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>(306) 244-0174</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>reception@simfc.ca</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>https://simfc.ca/</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>Paige Crozon, Living Skies Indigenous Basketball League Manager</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>Hosts Living Skies Indigenous Basketball League programming for Indigenous youth ages 11-17 (all youth welcome), in collaboration with Aboriginal Friendship Centres of Saskatchewan and One Love Basketball Inc.</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>Living Skies Indigenous Basketball League (LSIBL)</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>multi-sport / community org (Friendship Centre)</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>TeamLinkt (LSIBL registration)</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>https://simfc.ca/2022/05/25/living-skies-indigenous-basketball-league-for-indigenous-youth-ages-11-17/</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>LSIBL central coordinator: Paige Crozon, 306-955-0762, pcrozon@afcs.ca (league-level contact). LSIBL draws 700+ participants/60 coaches provincially; junior (U13/U15) Sept-Dec, senior (U18) Mar-Jun. | enriched 2026-07-18</t>
         </is>
@@ -6072,62 +6072,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>(306) 249-4712</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>https://smbayxe.ca</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>Greg Jockims — President (VP: Brad Smith; directors incl. Riley Daku, Sandy Bresciani, Kory Dawe)</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>Ages 5-18: Dunkaroos (5+), community association leagues, rep program (Sept evaluation camp, $60 tryout), Next Level Development League (NLDL), Jr/Sr girls and boys leagues, Elevate &amp; Excel spring program, HoopStart spring, 3x3 spring league, August summer camps</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>Saskatoon Minor Basketball Association (SMBA) — operates its own community and rep leagues; BSI Club Championships (Basketball Saskatchewan Provincials)</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>community nonprofit (city association / league operator)</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>TeamLinkt (leagues.teamlinkt.com/smba; legacy site smba.ca was a PHP league platform)</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
+      <c r="P87" t="inlineStr">
         <is>
           <t>https://smbayxe.ca/smba/AbouttheSMBA</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>The dominant youth basketball body in Saskatoon; SMBA is both a mapped league and the umbrella association. TeamLinkt customer — key competitive intel.</t>
         </is>
@@ -6144,62 +6144,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>306-693-5622</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>tanner@goldenticketsports.com</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>https://goldenticketsports.leagueapps.com/camps/3925409-saskatoon-public-schools-basketball-academy---2023-2024---grades-5-8</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>Golden Ticket Sports (operator; same outfit runs the mapped Moose Jaw Minor Basketball League — contact stephen@goldenticketbasketball.com on BSI registry)</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>Paid basketball academy programming for grades 5-8, delivered in partnership with Saskatoon Public Schools (2023-24 listing)</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>private academy program (school-division partnership; not a varsity team)</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>LeagueApps</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr">
+      <c r="P88" t="inlineStr">
         <is>
           <t>https://goldenticketsports.leagueapps.com/camps/3925409-saskatoon-public-schools-basketball-academy---2023-2024---grades-5-8</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>Most recent evidence is the 2023-24 LeagueApps listing — verify current status. LeagueApps usage by Golden Ticket = software competitive intel. | Private academy program (grades 5-8) run inside Saskatoon Public Schools facilities by Golden Ticket Sports Inc. Registration on LeagueApps (competitive intel): https://goldenticketsports.leagueapps.com/camps/3925409-saskatoon-public-schools-basketball-academy---2023-2024---grades-5-8 (portal requires login; program details gated). Operator contact from https://goldenticketsports.com/contact — email/phone above; operator HQ addresses: 2362 McGregor Place, Regina SK S4V 2Y4 and 1221 50 Ave, Lloydminster SK S9V 1Z7 (no Saskatoon street address — academy uses school gyms). Leadership from https://www.goldenticketsports.com/about-us: Brightman now also in Antwerp, Belgium with Elite Academy; King oversees Hoop Factory (Lloydminster); Greg Jockims (ex-USask Huskies coach) is the Saskatoon principal figure per https://www.goldenticketsports.com/about/greg-jockims. Also operates the Regina Catholic (RCSD) Basketball Academy — same model, expansion signal.</t>
         </is>
@@ -6216,57 +6216,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>saskatoonslam@gmail.com</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>https://saskatoonslam.com</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>Rep/club teams, boys and girls, U11/U13/U15/U17/U18; multiple teams per age (e.g. 3x U13 girls, 2x U15 girls, 2x U17 girls); hosts Prairie Season Opener tournament</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>BSI Club Championships / BSI-sanctioned spring club tournament circuit; BSI Club Championships (Basketball Saskatchewan Provincials); BSI-sanctioned spring club tournament circuit (2026)</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>community nonprofit (registered non-profit club)</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>WordPress.com website; registration platform not published</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>https://saskatoonslam.com/</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>One of Saskatoon's longest-running premier clubs. Tournament contact: saskatoonslamtourney@gmail.com. Board names not published on site.</t>
         </is>
@@ -6283,52 +6283,52 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>https://app.teamlinkt.com/register/go/saskatoonshadowbasketballclub/73399</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>Nonprofit boys club basketball, U11/U13/U15/U18; annual fall tryouts (2025-season tryout registration ran Sep 2-22, 2024)</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>BSI-sanctioned club tournament circuit; Genesis Basketball tournaments (entered as 'Saskatoon Shadow (Wiebe)')</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>TeamLinkt (registration)</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>https://app.teamlinkt.com/register/go/saskatoonshadowbasketballclub/73399</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>TeamLinkt customer — competitive intel. | Rep club, U11/U13/U15/U18. Incorporated as 'Saskatoon Shadow Basketball Inc' (D&amp;B listing exists: https://www.dnb.com/business-directory/company-profiles.saskatoon_shadow_basketball_inc.382d2a84b361f169a7c09d01a91b8ccd.html but principal not retrievable without account; SK corporate registry not free-searchable). No club website found — Facebook is main presence; IG @saskatoon_shadow_basketball. Registers on TeamLinkt (competitive intel): https://app.teamlinkt.com/register/go/saskatoonshadowbasketballclub/73399. A tournament entry 'Saskatoon Shadow (Wiebe)' at Genesis Basketball (https://genesisbasketball.leagueapps.com/tournaments/1025392/teams/2242546) suggests a coach surnamed Wiebe — UNCONFIRMED as principal. Not on Basketball Sask current-member list as of check.</t>
         </is>
@@ -6345,42 +6345,42 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>mitchellda1978@gmail.com</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>BSI-sanctioned club tournament circuit (inferred from BSI club membership)</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>club (structure unknown)</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="P91" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>Appears only on the BSI 2025/26 member registry under Saskatoon-based clubs; no web/social presence found. | Competitive club listed on the Basketball Saskatchewan current-member registry with contact email mitchellda1978@gmail.com (source: https://www.basketballsask.com/member-organizations/currentmembers). Email pattern suggests a contact surnamed Mitchell — UNCONFIRMED, so principal left empty. No website, social page, or registration portal found; PSO registry is the club's only verifiable footprint. 'Spartans Elite Basketball Club' (spartanselitebasketballclub.com) could not be confirmed as Saskatoon-related — do not merge.</t>
         </is>
@@ -6397,62 +6397,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>PO Box 32061 Erindale, Saskatoon, SK S7S 1N8</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>basketball@silverspringcommunity.ca</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>https://silverspringcommunity.ca/programs/basketball/</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>Adam Day — President</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>Community basketball program run in partnership with SMBA</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>Saskatoon Minor Basketball Association (SMBA)</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>community nonprofit (multi-sport community association)</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
+      <c r="P92" t="inlineStr">
         <is>
           <t>https://silverspringcommunity.ca/programs/basketball/</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>Evidence from association's basketball program page surfacing alongside SMBA community-league materials. | Type: community association youth program (plays in SMBA; SMBA registers via TeamLinkt — competitive intel). Basketball Coordinator: Paul Fraser (basketball@silverspringcommunity.ca; also listed on SMBA community-contacts page as paul.fraser.24@gmail.com); older program page named Brian Webb — appears superseded. President conflict: club's own executive-listing page says Adam Day (president@silverspringcommunity.ca), while City of Saskatoon 2025 CA contact list names Eli Wachniak — both documented, use with care. Sources: https://silverspringcommunity.ca/programs/basketball/ ; https://silverspringcommunity.ca/about-us/executive-listing/ ; https://smbayxe.ca/smba/CommunityBasketballContacts ; https://www.saskatoon.ca/sites/default/files/CA%20Contact%20List%20-%20Website%202025.pdf</t>
         </is>
@@ -6469,67 +6469,67 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>PO Box 23085, Market Mall, Saskatoon, SK S7J 5H3</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>ourstonebridge.programs@gmail.com</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>https://www.ourstonebridge.ca/</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>Alena Sherwood — President</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>SMBA registration for Mini &amp; Bantam divisions; spring basketball training in partnership with Houndsville Hoops; an SMBA team ('Stonebridge-Dobranski') has been fielded from the neighbourhood</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>Saskatoon Minor Basketball Association (SMBA)</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>community nonprofit (multi-sport community association)</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>TeamLinkt (SMBA registration)</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr">
+      <c r="P93" t="inlineStr">
         <is>
           <t>https://www.ourstonebridge.ca/smba-registration-mini-bantam/</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>Type: community association youth program (SMBA Mini &amp; Bantam registration; SMBA uses TeamLinkt — competitive intel; association memberships sold via Amilia). President Alena Sherwood confirmed in both Winter 2024 'Stonebridge Slate' newsletter and City of Saskatoon 2025 CA contact list (general email contactus@ourstonebridge.ca). Basketball coordinator per Winter 2024 newsletter: Vivian Balajonda; SMBA community-contacts page lists Dave &amp; Leah Deibert at ourstonebridge.programs@gmail.com (the address the club site routes basketball inquiries to). Sources: https://www.ourstonebridge.ca/ ; https://www.ourstonebridge.ca/wp-content/uploads/2024/11/SCA-Winter-2024-Newsletter-V1.pdf ; https://smbayxe.ca/smba/CommunityBasketballContacts ; https://www.saskatoon.ca/sites/default/files/CA%20Contact%20List%20-%20Website%202025.pdf</t>
         </is>
@@ -6546,52 +6546,52 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>stuttersteps.adrian@gmail.com</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>https://www.facebook.com/stuttersteps.bball/</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>Basketball player development and skill training</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>BSI Club Championships (Basketball Saskatchewan Provincials)</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>private academy / club (player development)</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>BSI 2025/26 member club in Saskatoon; web presence limited to Facebook/Instagram (@stuttersteps.bball). | Type: private skills-training/player-development program (academy-style). Confirmed current 2025/26 member of Basketball Saskatchewan Inc. (Saskatoon), but PSO registry lists only their Instagram (http://www.instagram.com/stuttersteps.bball/) — no contact person, email, or phone. Only web presence is Facebook (https://www.facebook.com/stuttersteps.bball/) and Instagram @stuttersteps.bball; Facebook About page is login-walled so contact fields could not be extracted. No owner/founder name found in news or registries. NOTE: stuttersteps.org (founder Davin Brar) is an unrelated US speech-therapy nonprofit — do not conflate. Sources: https://www.basketballsask.com/member-organizations/currentmembers ; https://www.instagram.com/stuttersteps.bball/</t>
         </is>
@@ -6608,62 +6608,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>info@basketballexperience.ca</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>https://www.basketballexperience.ca/</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>Jared Derkatz — founder / head coach</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t>Mini Hoopers (ages 2-4); co-ed ages 5-7 and 8-10; girls 8-15 beginner and 9-16 intermediate/advanced; boys 11-13 and 14-17; TBE 3x3 league; camps and clinics; open gyms; private 1-on-1 and semi-private training; athletic training</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t>TBE 3x3 league (own in-house league); TBE 3x3 Basketball League (self-operated)</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="N95" t="inlineStr">
         <is>
           <t>Registration through own website (no third-party platform identified)</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
+      <c r="O95" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr">
+      <c r="P95" t="inlineStr">
         <is>
           <t>https://www.basketballexperience.ca/</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
+      <c r="Q95" t="inlineStr">
         <is>
           <t>Private business focused on fundamentals and skill development for all ages/levels in Saskatoon and area.</t>
         </is>
@@ -6680,62 +6680,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>Saskatoon</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>info@yxeelitebasketball.com</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>https://www.yxeelitebasketball.com</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>Dion Dobranski — founder (founded club 2022; 30+ yrs playing/coaching incl. AAU in South Carolina)</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t>Boys and girls club teams with annual tryouts (2025-26 season); player development; runs the YXE Elite Summer Jam youth tournament in Saskatoon</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t>BSI-sanctioned club tournament circuit</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t>private club</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr">
+      <c r="N96" t="inlineStr">
         <is>
           <t>Bracketteam (used for YXE Elite Summer Jam event registration); club site is a coming-soon page</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr">
+      <c r="P96" t="inlineStr">
         <is>
           <t>https://www.yxeelitebasketball.com/</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr">
+      <c r="Q96" t="inlineStr">
         <is>
           <t>Founder attribution from UPREP Canada coach bio (page indexed in search; site itself now 404s).</t>
         </is>
@@ -6752,52 +6752,52 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>Saskatoon (unconfirmed)</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>info@uprepbasketball.com</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>https://www.uprepbasketball.com</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>Dwayne Selby (Founder &amp; President/Director of Basketball Operations)</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t>Nonprofit prep/club basketball for student-athletes; coaching staff includes Dion Dobranski (Saskatoon; also founder of YXE Elite)</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t>private prep club (self-described nonprofit)</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr">
+      <c r="O97" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr">
+      <c r="P97" t="inlineStr">
         <is>
           <t>https://www.uprepbasketball.com/</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr">
+      <c r="Q97" t="inlineStr">
         <is>
           <t>Website currently returns 404 on all pages; location inferred only from Saskatoon-based coach association (Dobranski also appears as an SMBA team coach on smba.ca). Verify before outreach. | LOCATION CORRECTION: NOT Saskatchewan — evidence places UPREP Canada in the Vancouver/Lower Mainland, BC area. Founder Dwayne Selby is a BC-based trainer (former Playmakers Basketball Training; head-coach listing at Capilano University, North Vancouver: https://athletics.capilanou.ca/sports/mbkb/2013-14/roster; LinkedIn: https://ca.linkedin.com/in/dwayne-selby-758096203). Site pages confirm 'Dwayne Selby — Founder and President of Basketball Operations' (https://www.uprepbasketball.com/dwayne-selby); other coach: Dion Dobranski. Nonprofit AAU travel-team club + 9-week academy program. Site blocks bot fetches (all pages 404 to WebFetch) — details taken from search-engine caches; IG @uprepcanada, X @uprepcanada. RECOMMEND: move this record from the Saskatchewan census to BC.</t>
         </is>
@@ -6814,57 +6814,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>St. Walburg</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>keljenlarre@gmail.com</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>Jen Larre — community coordinator</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="N98" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
+      <c r="O98" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr">
+      <c r="P98" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
@@ -6881,57 +6881,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>Swift Current</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>scminorbasketball@gmail.com</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>https://www.swiftcurrentsurge.ca/</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t>Nonprofit founded 2013; competitive 'Surge' rep teams with published tryouts for U11 boys, U15 girls, and Grade 9-12 boys; summer basketball camp; coach recruitment program; serves southwest Saskatchewan</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t>BSI Club Championships (Basketball Saskatchewan Provincials); BSI-sanctioned spring club tournament circuit (2026)</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="N99" t="inlineStr">
         <is>
           <t>Citrus Camps (register.citruscamps.com) for tryouts/programs; Google Forms for 2026 season registration</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr">
+      <c r="O99" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
+      <c r="P99" t="inlineStr">
         <is>
           <t>https://www.swiftcurrentsurge.ca/</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="Q99" t="inlineStr">
         <is>
           <t>BSI member. Board/president names not published on site. Twitter/X @SCsurgeBBALL</t>
         </is>
@@ -6948,57 +6948,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>Tisdale</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>recreation@tisdale.ca</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>Renae Reaume — community coordinator (Town of Tisdale recreation)</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site, town recreation dept)</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr">
+      <c r="N100" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr">
+      <c r="O100" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr">
+      <c r="P100" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
@@ -7015,57 +7015,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>Turtleford</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>marilyn.whelan@nwsd.ca</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>Marilyn Whelan — community coordinator</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="N101" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr">
+      <c r="O101" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O101" t="inlineStr">
+      <c r="P101" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
@@ -7082,57 +7082,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>Unity</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>billandcarin_leibel@live.ca</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>Carin Leibel — community coordinator</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="K102" t="inlineStr">
         <is>
           <t>Jr. NBA youth basketball program</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t>community program (Jr. NBA host site)</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr">
+      <c r="N102" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY league platform)</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr">
+      <c r="O102" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O102" t="inlineStr">
+      <c r="P102" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
@@ -7149,72 +7149,72 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>Various small towns, Saskatoon &amp; north region</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>2205 Victoria Avenue, Regina, SK S4P 0S4</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>(306) 780-9264</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>skybasketball@sasktel.net</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>Per-town volunteer coordinators (named with emails on the SKY communities page)</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>Jr. NBA grassroots programs (typically Gr1-6) run by town rec departments, school-division staff and volunteers under the SKY Basketball umbrella</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t>community program network (league-operated, not independent clubs)</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
+      <c r="N103" t="inlineStr">
         <is>
           <t>TeamLinkt (SKY Basketball league platform)</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr">
+      <c r="O103" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O103" t="inlineStr">
+      <c r="P103" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/skybasketball/Communities</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr">
+      <c r="Q103" t="inlineStr">
         <is>
           <t>These are program sites of the already-mapped SKY league, not standalone clubs — captured here as the complete small-town basketball footprint for this region; coordinator emails are published at the source URL. Several coordinators are town recreation departments (Biggar, Tisdale, Nipawin) or school divisions (NWSD, NESD, NLSD). | Not an independent club: Jr. NBA-branded rural program run centrally by the PSO Basketball Saskatchewan Inc. from its Regina office, delivered by local volunteer coordinators in 40+ communities (grades 3-6, ~10-12 practices + spring tournament; areas incl. Melfort, Parkland, North Battleford, Outlook, Swift Current, Weyburn, Yorkton). COMPETITIVE INTEL: registration/site runs on TeamLinkt (skybasketball.ca = leagues.teamlinkt.com/skybasketball). Community-coordinator contacts only released post-registration. Sources: https://www.skybasketball.ca/skybasketball/ContactUs, https://www.basketballsask.com/players/skyjrnba. Type: community association network (PSO-operated).</t>
         </is>
@@ -7231,62 +7231,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>Warman</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>smba4712@gmail.com</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t>https://leagues.teamlinkt.com/smba</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>Scott Campbell, Contact Person</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>Youth basketball run through the Saskatoon Minor Basketball Association for Warman kids; Warman/Martensville players also eligible for SMBA NLDL tryouts</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t>Saskatoon Minor Basketball Association (SMBA)</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t>community program (SMBA-operated)</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
+      <c r="N104" t="inlineStr">
         <is>
           <t>TeamLinkt</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr">
+      <c r="O104" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O104" t="inlineStr">
+      <c r="P104" t="inlineStr">
         <is>
           <t>https://www.warman.ca/892/Warman-Minor-Basketball</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
+      <c r="Q104" t="inlineStr">
         <is>
           <t>Not independently operated — administered by SMBA per City of Warman directory. | enriched 2026-07-18</t>
         </is>
@@ -7303,57 +7303,57 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>Saskatoon &amp; north (SK)</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>Warman</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>warmanwolves@gmail.com</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t>https://www.warman.ca/891/Warman-Wolves-Basketball-Club</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>Scott Campbell — club contact</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>Organized club practices and tournament play for children, January through end of June; tryout-based club teams ('newest club' launched January per Facebook)</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t>BSI Club Championships (Basketball Saskatchewan Provincials); BSI-sanctioned spring club tournament circuit (2026); BSI-sanctioned club tournament circuit (BSI member club; specific leagues not published)</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t>community nonprofit (volunteer parent-run club)</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr">
+      <c r="O105" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr">
+      <c r="P105" t="inlineStr">
         <is>
           <t>https://www.warman.ca/891/Warman-Wolves-Basketball-Club</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
+      <c r="Q105" t="inlineStr">
         <is>
           <t>BSI 2025/26 member ('Warman Wolves'); listed on City of Warman community groups directory; Facebook page id 61562776302881.</t>
         </is>
@@ -7370,62 +7370,62 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>Regina &amp; south, SK</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>Weyburn</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>h.souledge@gmail.com</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t>https://www.facebook.com/p/Weyburn-Youth-Basketball-100068064164988/</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>Hannah Paterson — Weyburn Jr. NBA coordinator</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t>Community Jr. NBA program (partnership with Basketball Saskatchewan/Canada Basketball) for Gr 1-6: Gr 1-2 combined, Gr 3/4 and 5/6 split boys/girls; volunteer-coached</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t>SKY Basketball / Saskatchewan Youth Basketball (Jr. NBA)</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr">
+      <c r="N106" t="inlineStr">
         <is>
           <t>TeamLinkt (app.teamlinkt.com/register/go/skybasketball/83706)</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr">
+      <c r="O106" t="inlineStr">
         <is>
           <t>reported</t>
         </is>
       </c>
-      <c r="O106" t="inlineStr">
+      <c r="P106" t="inlineStr">
         <is>
           <t>https://discoverweyburn.com/articles/registrations-open-for-weyburn-youth-basketballs-junior-nba-program-</t>
         </is>
       </c>
-      <c r="P106" t="inlineStr">
+      <c r="Q106" t="inlineStr">
         <is>
           <t>No standalone rep club found in Weyburn — rep-level players join Estevan Club Basketball per Estevan news coverage.</t>
         </is>
@@ -7442,73 +7442,73 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>Yorkton</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>306-621-2595</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>jason@goldenticketsports.com</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t>https://yorktonbluejays.ca/</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t>Jason Payne — general inquiries/lead contact (club founded 2016); Ryley Wawryk — U13 program; Chad McDowell — U15 program</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t>Founded 2016 to give Yorkton-area youth competitive basketball outside the school season; 2026 season: U13 and U15 boys teams; sessions half skill development / half gameplay; equal playing time through 3 quarters; hosts club basketball tournament</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t>BSI Club Championships (Basketball Saskatchewan Provincials); BSI-sanctioned spring club tournament circuit (2026)</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t>community club (rep)</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr">
+      <c r="N107" t="inlineStr">
         <is>
           <t>TeamLinkt (site 'Powered by TeamLinkt'; registration app.teamlinkt.com/register/go/yorktonbluejays); legacy site on RAMP InterActive (bluejaysbasketball.ca)</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr">
+      <c r="O107" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O107" t="inlineStr">
+      <c r="P107" t="inlineStr">
         <is>
           <t>https://yorktonbluejays.ca/</t>
         </is>
       </c>
-      <c r="P107" t="inlineStr">
+      <c r="Q107" t="inlineStr">
         <is>
           <t>Program administered with Golden Ticket Sports (contact Jason Payne). Legion-sponsored ('Yorkton Legion Blue Jays'). Migrated RAMP → TeamLinkt = software-switch intel | Also listed as: Yorkton Blue Jays Basketball Club</t>
         </is>
-      </c>
-      <c r="Q107" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -7522,42 +7522,42 @@
           <t>Saskatchewan</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>Regina &amp; south Saskatchewan</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>Yorkton</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="H108" t="inlineStr">
         <is>
           <t>darcy_zaharia@hotmail.com</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="K108" t="inlineStr">
         <is>
           <t>U13 girls community team; first season completed June 2026 (exhibition vs U13 boys Blue Jays); sponsored by Harvest Meats; coach Johanna Fleger; also runs Harvest Hotshots basketball camp</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr">
+      <c r="O108" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O108" t="inlineStr">
+      <c r="P108" t="inlineStr">
         <is>
           <t>https://www.basketballsask.com/member-organizations/currentmembers</t>
         </is>
       </c>
-      <c r="P108" t="inlineStr">
+      <c r="Q108" t="inlineStr">
         <is>
           <t>Separate BSI member entry from Blue Jays but operationally intertwined; registry contact Darcy Zaharia (role not stated) | Also listed as: Yorkton Hotshots</t>
         </is>
